--- a/BURL.xlsx
+++ b/BURL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2FCFB2-09CE-4749-819D-1EFB28292E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA114C6-7683-490D-9700-D727BF323D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>Burlington Store</t>
   </si>
@@ -197,6 +197,9 @@
   <si>
     <t>Q423</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -283,7 +286,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -302,6 +305,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -658,7 +662,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>252.2</v>
+        <v>304.51</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -666,10 +670,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="6">
-        <v>62.927005999999999</v>
+        <v>62.687426000000002</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -681,7 +685,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>15870.190913199998</v>
+        <v>19088.948091260001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -695,7 +699,7 @@
         <v>584.07899999999995</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -707,7 +711,7 @@
         <v>2035.424</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -716,7 +720,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>17321.535913199998</v>
+        <v>20540.293091259999</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -806,6 +810,9 @@
       <c r="V2" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="W2" s="11" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="3" spans="1:58" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -823,14 +830,14 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="T3" s="2">
-        <v>840</v>
-      </c>
       <c r="U3" s="2">
-        <v>927</v>
+        <v>1107</v>
       </c>
       <c r="V3" s="2">
-        <v>1007</v>
+        <v>1108</v>
+      </c>
+      <c r="W3" s="2">
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.2">
@@ -881,9 +888,15 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
+      <c r="U5" s="6">
+        <v>9708.973</v>
+      </c>
+      <c r="V5" s="6">
+        <v>10616.743</v>
+      </c>
+      <c r="W5" s="6">
+        <v>11549.607</v>
+      </c>
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
@@ -954,9 +967,15 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
+      <c r="U6" s="6">
+        <v>18.494</v>
+      </c>
+      <c r="V6" s="6">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="W6" s="6">
+        <v>17.303000000000001</v>
+      </c>
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
@@ -1048,9 +1067,18 @@
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
+      <c r="U7" s="7">
+        <f t="shared" ref="U7:V7" si="1">+U5+U6</f>
+        <v>9727.4670000000006</v>
+      </c>
+      <c r="V7" s="7">
+        <f t="shared" si="1"/>
+        <v>10634.823</v>
+      </c>
+      <c r="W7" s="7">
+        <f>+W5+W6</f>
+        <v>11566.91</v>
+      </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
@@ -1121,9 +1149,15 @@
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
+      <c r="U8" s="6">
+        <v>5584.06</v>
+      </c>
+      <c r="V8" s="6">
+        <v>6025.2719999999999</v>
+      </c>
+      <c r="W8" s="6">
+        <v>6486.9219999999996</v>
+      </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
@@ -1165,27 +1199,27 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <f t="shared" ref="C9:H9" si="1">+C7-C8</f>
+        <f t="shared" ref="C9:H9" si="2">+C7-C8</f>
         <v>0</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>991.54099999999949</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1030.8270000000002</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="6">
@@ -1193,31 +1227,55 @@
         <v>1112.5529999999999</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" ref="J9:M9" si="2">+J7-J8</f>
+        <f t="shared" ref="J9:M9" si="3">+J7-J8</f>
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1098.9290000000001</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1185.442</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1200.587</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
+      <c r="P9" s="6">
+        <f t="shared" ref="P9:W9" si="4">+P7-P8</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="4"/>
+        <v>4143.4070000000002</v>
+      </c>
+      <c r="V9" s="6">
+        <f t="shared" si="4"/>
+        <v>4609.5510000000004</v>
+      </c>
+      <c r="W9" s="6">
+        <f t="shared" si="4"/>
+        <v>5079.9880000000003</v>
+      </c>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
@@ -1288,9 +1346,15 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
+      <c r="U10" s="6">
+        <v>3288.3150000000001</v>
+      </c>
+      <c r="V10" s="6">
+        <v>3546.9670000000001</v>
+      </c>
+      <c r="W10" s="6">
+        <v>3817.18</v>
+      </c>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
@@ -1361,9 +1425,15 @@
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
+      <c r="U11" s="6">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="V11" s="6">
+        <v>4.5529999999999999</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.112</v>
+      </c>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
@@ -1434,9 +1504,15 @@
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
+      <c r="U12" s="6">
+        <v>307.06400000000002</v>
+      </c>
+      <c r="V12" s="6">
+        <v>347.57499999999999</v>
+      </c>
+      <c r="W12" s="6">
+        <v>417.87099999999998</v>
+      </c>
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
@@ -1507,9 +1583,15 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
+      <c r="U13" s="6">
+        <v>6.367</v>
+      </c>
+      <c r="V13" s="6">
+        <v>12.920999999999999</v>
+      </c>
+      <c r="W13" s="6">
+        <v>9.8569999999999993</v>
+      </c>
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
@@ -1580,9 +1662,15 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
+      <c r="U14" s="6">
+        <v>16.248999999999999</v>
+      </c>
+      <c r="V14" s="6">
+        <v>16.693999999999999</v>
+      </c>
+      <c r="W14" s="6">
+        <v>31.286999999999999</v>
+      </c>
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
@@ -1624,27 +1712,27 @@
         <v>25</v>
       </c>
       <c r="C15" s="6">
-        <f t="shared" ref="C15:H15" si="3">+C9-SUM(C10:C13)+C14</f>
+        <f t="shared" ref="C15:H15" si="5">+C9-SUM(C10:C13)+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100.20199999999953</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>126.28800000000015</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I15" s="6">
@@ -1652,31 +1740,55 @@
         <v>137.23899999999986</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" ref="J15:M15" si="4">+J9-SUM(J10:J13)+J14</f>
+        <f t="shared" ref="J15:M15" si="6">+J9-SUM(J10:J13)+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>148.68200000000016</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>144.75100000000009</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>152.309</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
+      <c r="P15" s="6">
+        <f t="shared" ref="P15:W15" si="7">+P9-SUM(P10:P13)+P14</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" si="7"/>
+        <v>557.81299999999987</v>
+      </c>
+      <c r="V15" s="6">
+        <f t="shared" si="7"/>
+        <v>714.22900000000072</v>
+      </c>
+      <c r="W15" s="6">
+        <f t="shared" si="7"/>
+        <v>866.25500000000079</v>
+      </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
@@ -1747,9 +1859,15 @@
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
+      <c r="U16" s="6">
+        <v>38.274000000000001</v>
+      </c>
+      <c r="V16" s="6">
+        <v>1.4119999999999999</v>
+      </c>
+      <c r="W16" s="6">
+        <v>0</v>
+      </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
@@ -1821,9 +1939,18 @@
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
+      <c r="U17" s="6">
+        <f>-24.633+78.399</f>
+        <v>53.766000000000005</v>
+      </c>
+      <c r="V17" s="6">
+        <f>69.522-31.519</f>
+        <v>38.003000000000007</v>
+      </c>
+      <c r="W17" s="6">
+        <f>71.041-20.904</f>
+        <v>50.137</v>
+      </c>
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
@@ -1865,27 +1992,27 @@
         <v>28</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" ref="C18:H18" si="5">+C15-C16-C17</f>
+        <f t="shared" ref="C18:H18" si="8">+C15-C16-C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>66.891999999999541</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>109.63900000000015</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I18" s="6">
@@ -1893,31 +2020,55 @@
         <v>118.05799999999985</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" ref="J18:M18" si="6">+J15-J16-J17</f>
+        <f t="shared" ref="J18:M18" si="9">+J15-J16-J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>132.87200000000016</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>127.3240000000001</v>
       </c>
       <c r="M18" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>138.059</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
+      <c r="P18" s="6">
+        <f t="shared" ref="P18:W18" si="10">+P15-P16-P17</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" si="10"/>
+        <v>465.77299999999985</v>
+      </c>
+      <c r="V18" s="6">
+        <f t="shared" si="10"/>
+        <v>674.81400000000065</v>
+      </c>
+      <c r="W18" s="6">
+        <f t="shared" si="10"/>
+        <v>816.11800000000085</v>
+      </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
@@ -1988,9 +2139,15 @@
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
+      <c r="U19" s="6">
+        <v>126.124</v>
+      </c>
+      <c r="V19" s="6">
+        <v>171.17500000000001</v>
+      </c>
+      <c r="W19" s="6">
+        <v>205.965</v>
+      </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
@@ -2032,27 +2189,27 @@
         <v>29</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:H20" si="7">+C18-C19</f>
+        <f t="shared" ref="C20:H20" si="11">+C18-C19</f>
         <v>0</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>48.55099999999954</v>
       </c>
       <c r="F20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>78.514000000000152</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I20" s="6">
@@ -2060,31 +2217,55 @@
         <v>90.616999999999848</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" ref="J20:M20" si="8">+J18-J19</f>
+        <f t="shared" ref="J20:M20" si="12">+J18-J19</f>
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>100.83300000000015</v>
       </c>
       <c r="L20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>94.185000000000088</v>
       </c>
       <c r="M20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>104.75</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
+      <c r="P20" s="6">
+        <f t="shared" ref="P20:W20" si="13">+P18-P19</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="6">
+        <f t="shared" si="13"/>
+        <v>339.64899999999989</v>
+      </c>
+      <c r="V20" s="6">
+        <f t="shared" si="13"/>
+        <v>503.63900000000064</v>
+      </c>
+      <c r="W20" s="6">
+        <f t="shared" si="13"/>
+        <v>610.15300000000082</v>
+      </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
@@ -2184,27 +2365,27 @@
         <v>30</v>
       </c>
       <c r="C22" s="6" t="e">
-        <f t="shared" ref="C22:H22" si="9">+C20/C23</f>
+        <f t="shared" ref="C22:H22" si="14">+C20/C23</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D22" s="6" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0.75032067627922083</v>
       </c>
       <c r="F22" s="6" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>1.229258975121732</v>
       </c>
       <c r="H22" s="6" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I22" s="6">
@@ -2212,19 +2393,19 @@
         <v>1.4256249705017046</v>
       </c>
       <c r="J22" s="6" t="e">
-        <f t="shared" ref="J22:M22" si="10">+J20/J23</f>
+        <f t="shared" ref="J22:M22" si="15">+J20/J23</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.5982912756784198</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.4741051445385267</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1.6631736051570289</v>
       </c>
       <c r="N22" s="6"/>
@@ -2234,9 +2415,18 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
+      <c r="U22" s="12">
+        <f t="shared" ref="U22:V22" si="16">+U20/U23</f>
+        <v>5.2518709797130114</v>
+      </c>
+      <c r="V22" s="12">
+        <f t="shared" si="16"/>
+        <v>7.9146211144985488</v>
+      </c>
+      <c r="W22" s="12">
+        <f>+W20/W23</f>
+        <v>9.6874285532833859</v>
+      </c>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
@@ -2307,9 +2497,15 @@
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
+      <c r="U23" s="6">
+        <v>64.671999999999997</v>
+      </c>
+      <c r="V23" s="6">
+        <v>63.634</v>
+      </c>
+      <c r="W23" s="6">
+        <v>62.984000000000002</v>
+      </c>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
       <c r="Z23" s="6"/>
@@ -2413,11 +2609,11 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="8" t="e">
-        <f t="shared" ref="G25:H25" si="11">+G7/C7-1</f>
+        <f t="shared" ref="G25:H25" si="17">+G7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="8" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="8">
@@ -2491,27 +2687,27 @@
         <v>32</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:H26" si="12">+C10/C7</f>
+        <f t="shared" ref="C26:H26" si="18">+C10/C7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.3611607856566898</v>
       </c>
       <c r="F26" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.34944208323929205</v>
       </c>
       <c r="H26" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="9">
@@ -2585,27 +2781,27 @@
         <v>33</v>
       </c>
       <c r="C27" s="9" t="e">
-        <f t="shared" ref="C27:H27" si="13">+C15/C7</f>
+        <f t="shared" ref="C27:H27" si="19">+C15/C7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="9" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>4.3768831797377741E-2</v>
       </c>
       <c r="F27" s="9" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>5.347667403611104E-2</v>
       </c>
       <c r="H27" s="9" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="9">
@@ -2679,27 +2875,27 @@
         <v>34</v>
       </c>
       <c r="C28" s="9" t="e">
-        <f t="shared" ref="C28:H28" si="14">+C19/C18</f>
+        <f t="shared" ref="C28:H28" si="20">+C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.27418824373617362</v>
       </c>
       <c r="F28" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.28388620837475675</v>
       </c>
       <c r="H28" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="9">

--- a/BURL.xlsx
+++ b/BURL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA114C6-7683-490D-9700-D727BF323D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1980BE80-244E-4E7E-BE5D-44D7E5825596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Burlington Store</t>
   </si>
@@ -200,6 +200,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -208,13 +220,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -283,29 +301,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -662,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>304.51</v>
+        <v>358.03</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -670,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="6">
-        <v>62.687426000000002</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>48</v>
+        <v>62.942205999999999</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -685,7 +706,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>19088.948091260001</v>
+        <v>22535.198014179998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -696,10 +717,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>584.07899999999995</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>48</v>
+        <v>747.35500000000002</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -707,11 +728,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="3">
-        <f>2015.471+19.953</f>
-        <v>2035.424</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>48</v>
+        <f>20.02+1897.343</f>
+        <v>1917.3630000000001</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -720,7 +741,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>20540.293091259999</v>
+        <v>23705.206014179999</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -739,7 +760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7958BF-2B17-4548-B028-78081AE6CD78}">
-  <dimension ref="A1:BF238"/>
+  <dimension ref="A1:BJ238"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -747,12 +768,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.2">
       <c r="C2" s="10" t="s">
         <v>49</v>
       </c>
@@ -789,32 +810,44 @@
       <c r="N2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -830,17 +863,21 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="U3" s="2">
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="Y3" s="2">
         <v>1107</v>
       </c>
-      <c r="V3" s="2">
+      <c r="Z3" s="2">
         <v>1108</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AA3" s="2">
         <v>1212</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.2">
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -853,8 +890,12 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
@@ -882,25 +923,27 @@
         <v>2706.0030000000002</v>
       </c>
       <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="O5" s="6">
+        <v>2852.31</v>
+      </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
-      <c r="U5" s="6">
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6">
         <v>9708.973</v>
       </c>
-      <c r="V5" s="6">
+      <c r="Z5" s="6">
         <v>10616.743</v>
       </c>
-      <c r="W5" s="6">
+      <c r="AA5" s="6">
         <v>11549.607</v>
       </c>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
       <c r="AD5" s="6"/>
@@ -931,9 +974,13 @@
       <c r="BC5" s="6"/>
       <c r="BD5" s="6"/>
       <c r="BE5" s="6"/>
-      <c r="BF5" s="3"/>
-    </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF5" s="6"/>
+      <c r="BG5" s="6"/>
+      <c r="BH5" s="6"/>
+      <c r="BI5" s="6"/>
+      <c r="BJ5" s="3"/>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
@@ -961,25 +1008,27 @@
         <v>4.4370000000000003</v>
       </c>
       <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="O6" s="6">
+        <v>4.1509999999999998</v>
+      </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
-      <c r="U6" s="6">
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6">
         <v>18.494</v>
       </c>
-      <c r="V6" s="6">
+      <c r="Z6" s="6">
         <v>18.079999999999998</v>
       </c>
-      <c r="W6" s="6">
+      <c r="AA6" s="6">
         <v>17.303000000000001</v>
       </c>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
@@ -1010,9 +1059,13 @@
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
-      <c r="BF6" s="3"/>
-    </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF6" s="6"/>
+      <c r="BG6" s="6"/>
+      <c r="BH6" s="6"/>
+      <c r="BI6" s="6"/>
+      <c r="BJ6" s="3"/>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1060,29 +1113,35 @@
         <f>+M5+M6</f>
         <v>2710.44</v>
       </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="N7" s="7">
+        <f t="shared" ref="N7:O7" si="1">+N5+N6</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="1"/>
+        <v>2856.4609999999998</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
-      <c r="U7" s="7">
-        <f t="shared" ref="U7:V7" si="1">+U5+U6</f>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7">
+        <f t="shared" ref="Y7:Z7" si="2">+Y5+Y6</f>
         <v>9727.4670000000006</v>
       </c>
-      <c r="V7" s="7">
-        <f t="shared" si="1"/>
+      <c r="Z7" s="7">
+        <f t="shared" si="2"/>
         <v>10634.823</v>
       </c>
-      <c r="W7" s="7">
-        <f>+W5+W6</f>
+      <c r="AA7" s="7">
+        <f>+AA5+AA6</f>
         <v>11566.91</v>
       </c>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
       <c r="AB7" s="6"/>
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
@@ -1113,9 +1172,13 @@
       <c r="BC7" s="6"/>
       <c r="BD7" s="6"/>
       <c r="BE7" s="6"/>
-      <c r="BF7" s="3"/>
-    </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF7" s="6"/>
+      <c r="BG7" s="6"/>
+      <c r="BH7" s="6"/>
+      <c r="BI7" s="6"/>
+      <c r="BJ7" s="3"/>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1143,25 +1206,27 @@
         <v>1509.8530000000001</v>
       </c>
       <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <v>1594.8040000000001</v>
+      </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
-      <c r="U8" s="6">
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6">
         <v>5584.06</v>
       </c>
-      <c r="V8" s="6">
+      <c r="Z8" s="6">
         <v>6025.2719999999999</v>
       </c>
-      <c r="W8" s="6">
+      <c r="AA8" s="6">
         <v>6486.9219999999996</v>
       </c>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
       <c r="AB8" s="6"/>
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
@@ -1192,34 +1257,38 @@
       <c r="BC8" s="6"/>
       <c r="BD8" s="6"/>
       <c r="BE8" s="6"/>
-      <c r="BF8" s="3"/>
-    </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF8" s="6"/>
+      <c r="BG8" s="6"/>
+      <c r="BH8" s="6"/>
+      <c r="BI8" s="6"/>
+      <c r="BJ8" s="3"/>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <f t="shared" ref="C9:H9" si="2">+C7-C8</f>
+        <f t="shared" ref="C9:H9" si="3">+C7-C8</f>
         <v>0</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>991.54099999999949</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1030.8270000000002</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I9" s="6">
@@ -1227,59 +1296,65 @@
         <v>1112.5529999999999</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" ref="J9:M9" si="3">+J7-J8</f>
+        <f t="shared" ref="J9:O9" si="4">+J7-J8</f>
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1098.9290000000001</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1185.442</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1200.587</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6">
-        <f t="shared" ref="P9:W9" si="4">+P7-P8</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="N9" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R9" s="6">
+      <c r="O9" s="6">
         <f t="shared" si="4"/>
+        <v>1261.6569999999997</v>
+      </c>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6">
+        <f t="shared" ref="T9:AA9" si="5">+T7-T8</f>
         <v>0</v>
       </c>
-      <c r="S9" s="6">
-        <f t="shared" si="4"/>
+      <c r="U9" s="6">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T9" s="6">
-        <f t="shared" si="4"/>
+      <c r="V9" s="6">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U9" s="6">
-        <f t="shared" si="4"/>
+      <c r="W9" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="6">
+        <f t="shared" si="5"/>
         <v>4143.4070000000002</v>
       </c>
-      <c r="V9" s="6">
-        <f t="shared" si="4"/>
+      <c r="Z9" s="6">
+        <f t="shared" si="5"/>
         <v>4609.5510000000004</v>
       </c>
-      <c r="W9" s="6">
-        <f t="shared" si="4"/>
+      <c r="AA9" s="6">
+        <f t="shared" si="5"/>
         <v>5079.9880000000003</v>
       </c>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
@@ -1310,9 +1385,13 @@
       <c r="BC9" s="6"/>
       <c r="BD9" s="6"/>
       <c r="BE9" s="6"/>
-      <c r="BF9" s="3"/>
-    </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF9" s="6"/>
+      <c r="BG9" s="6"/>
+      <c r="BH9" s="6"/>
+      <c r="BI9" s="6"/>
+      <c r="BJ9" s="3"/>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1340,25 +1419,27 @@
         <v>947.51800000000003</v>
       </c>
       <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="6">
+        <v>989.37400000000002</v>
+      </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6">
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6">
         <v>3288.3150000000001</v>
       </c>
-      <c r="V10" s="6">
+      <c r="Z10" s="6">
         <v>3546.9670000000001</v>
       </c>
-      <c r="W10" s="6">
+      <c r="AA10" s="6">
         <v>3817.18</v>
       </c>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
       <c r="AC10" s="6"/>
       <c r="AD10" s="6"/>
@@ -1389,9 +1470,13 @@
       <c r="BC10" s="6"/>
       <c r="BD10" s="6"/>
       <c r="BE10" s="6"/>
-      <c r="BF10" s="3"/>
-    </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF10" s="6"/>
+      <c r="BG10" s="6"/>
+      <c r="BH10" s="6"/>
+      <c r="BI10" s="6"/>
+      <c r="BJ10" s="3"/>
+    </row>
+    <row r="11" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1419,25 +1504,27 @@
         <v>0</v>
       </c>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6">
+        <v>15.315</v>
+      </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
-      <c r="U11" s="6">
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="V11" s="6">
+      <c r="Z11" s="6">
         <v>4.5529999999999999</v>
       </c>
-      <c r="W11" s="6">
+      <c r="AA11" s="6">
         <v>0.112</v>
       </c>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
       <c r="AD11" s="6"/>
@@ -1468,9 +1555,13 @@
       <c r="BC11" s="6"/>
       <c r="BD11" s="6"/>
       <c r="BE11" s="6"/>
-      <c r="BF11" s="3"/>
-    </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF11" s="6"/>
+      <c r="BG11" s="6"/>
+      <c r="BH11" s="6"/>
+      <c r="BI11" s="6"/>
+      <c r="BJ11" s="3"/>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1498,25 +1589,27 @@
         <v>99.283000000000001</v>
       </c>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="6">
+        <v>104.607</v>
+      </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
-      <c r="U12" s="6">
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6">
         <v>307.06400000000002</v>
       </c>
-      <c r="V12" s="6">
+      <c r="Z12" s="6">
         <v>347.57499999999999</v>
       </c>
-      <c r="W12" s="6">
+      <c r="AA12" s="6">
         <v>417.87099999999998</v>
       </c>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
       <c r="AC12" s="6"/>
       <c r="AD12" s="6"/>
@@ -1547,9 +1640,13 @@
       <c r="BC12" s="6"/>
       <c r="BD12" s="6"/>
       <c r="BE12" s="6"/>
-      <c r="BF12" s="3"/>
-    </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF12" s="6"/>
+      <c r="BG12" s="6"/>
+      <c r="BH12" s="6"/>
+      <c r="BI12" s="6"/>
+      <c r="BJ12" s="3"/>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
@@ -1577,25 +1674,27 @@
         <v>3.786</v>
       </c>
       <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>0.80700000000000005</v>
+      </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
-      <c r="U13" s="6">
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6">
         <v>6.367</v>
       </c>
-      <c r="V13" s="6">
+      <c r="Z13" s="6">
         <v>12.920999999999999</v>
       </c>
-      <c r="W13" s="6">
+      <c r="AA13" s="6">
         <v>9.8569999999999993</v>
       </c>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
@@ -1626,9 +1725,13 @@
       <c r="BC13" s="6"/>
       <c r="BD13" s="6"/>
       <c r="BE13" s="6"/>
-      <c r="BF13" s="3"/>
-    </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF13" s="6"/>
+      <c r="BG13" s="6"/>
+      <c r="BH13" s="6"/>
+      <c r="BI13" s="6"/>
+      <c r="BJ13" s="3"/>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1656,25 +1759,27 @@
         <v>2.3090000000000002</v>
       </c>
       <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
+      <c r="O14" s="6">
+        <v>1.4490000000000001</v>
+      </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="6">
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6">
         <v>16.248999999999999</v>
       </c>
-      <c r="V14" s="6">
+      <c r="Z14" s="6">
         <v>16.693999999999999</v>
       </c>
-      <c r="W14" s="6">
+      <c r="AA14" s="6">
         <v>31.286999999999999</v>
       </c>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
       <c r="AC14" s="6"/>
       <c r="AD14" s="6"/>
@@ -1705,34 +1810,38 @@
       <c r="BC14" s="6"/>
       <c r="BD14" s="6"/>
       <c r="BE14" s="6"/>
-      <c r="BF14" s="3"/>
-    </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF14" s="6"/>
+      <c r="BG14" s="6"/>
+      <c r="BH14" s="6"/>
+      <c r="BI14" s="6"/>
+      <c r="BJ14" s="3"/>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6">
-        <f t="shared" ref="C15:H15" si="5">+C9-SUM(C10:C13)+C14</f>
+        <f t="shared" ref="C15:H15" si="6">+C9-SUM(C10:C13)+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>100.20199999999953</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>126.28800000000015</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I15" s="6">
@@ -1740,59 +1849,65 @@
         <v>137.23899999999986</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" ref="J15:M15" si="6">+J9-SUM(J10:J13)+J14</f>
+        <f t="shared" ref="J15:O15" si="7">+J9-SUM(J10:J13)+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>148.68200000000016</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>144.75100000000009</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>152.309</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6">
-        <f t="shared" ref="P15:W15" si="7">+P9-SUM(P10:P13)+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
+      <c r="N15" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R15" s="6">
+      <c r="O15" s="6">
         <f t="shared" si="7"/>
+        <v>153.00299999999964</v>
+      </c>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6">
+        <f t="shared" ref="T15:AA15" si="8">+T9-SUM(T10:T13)+T14</f>
         <v>0</v>
       </c>
-      <c r="S15" s="6">
-        <f t="shared" si="7"/>
+      <c r="U15" s="6">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T15" s="6">
-        <f t="shared" si="7"/>
+      <c r="V15" s="6">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U15" s="6">
-        <f t="shared" si="7"/>
+      <c r="W15" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="6">
+        <f t="shared" si="8"/>
         <v>557.81299999999987</v>
       </c>
-      <c r="V15" s="6">
-        <f t="shared" si="7"/>
+      <c r="Z15" s="6">
+        <f t="shared" si="8"/>
         <v>714.22900000000072</v>
       </c>
-      <c r="W15" s="6">
-        <f t="shared" si="7"/>
+      <c r="AA15" s="6">
+        <f t="shared" si="8"/>
         <v>866.25500000000079</v>
       </c>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
       <c r="AD15" s="6"/>
@@ -1823,9 +1938,13 @@
       <c r="BC15" s="6"/>
       <c r="BD15" s="6"/>
       <c r="BE15" s="6"/>
-      <c r="BF15" s="3"/>
-    </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.2">
+      <c r="BF15" s="6"/>
+      <c r="BG15" s="6"/>
+      <c r="BH15" s="6"/>
+      <c r="BI15" s="6"/>
+      <c r="BJ15" s="3"/>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1853,25 +1972,27 @@
         <v>0</v>
       </c>
       <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
-      <c r="U16" s="6">
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6">
         <v>38.274000000000001</v>
       </c>
-      <c r="V16" s="6">
+      <c r="Z16" s="6">
         <v>1.4119999999999999</v>
       </c>
-      <c r="W16" s="6">
+      <c r="AA16" s="6">
         <v>0</v>
       </c>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
       <c r="AB16" s="6"/>
       <c r="AC16" s="6"/>
       <c r="AD16" s="6"/>
@@ -1902,9 +2023,13 @@
       <c r="BC16" s="6"/>
       <c r="BD16" s="6"/>
       <c r="BE16" s="6"/>
-      <c r="BF16" s="3"/>
-    </row>
-    <row r="17" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF16" s="6"/>
+      <c r="BG16" s="6"/>
+      <c r="BH16" s="6"/>
+      <c r="BI16" s="6"/>
+      <c r="BJ16" s="3"/>
+    </row>
+    <row r="17" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
@@ -1933,28 +2058,31 @@
         <v>14.25</v>
       </c>
       <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="O17" s="6">
+        <f>16.495-6.161</f>
+        <v>10.334000000000001</v>
+      </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
-      <c r="U17" s="6">
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6">
         <f>-24.633+78.399</f>
         <v>53.766000000000005</v>
       </c>
-      <c r="V17" s="6">
+      <c r="Z17" s="6">
         <f>69.522-31.519</f>
         <v>38.003000000000007</v>
       </c>
-      <c r="W17" s="6">
+      <c r="AA17" s="6">
         <f>71.041-20.904</f>
         <v>50.137</v>
       </c>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
       <c r="AB17" s="6"/>
       <c r="AC17" s="6"/>
       <c r="AD17" s="6"/>
@@ -1985,34 +2113,38 @@
       <c r="BC17" s="6"/>
       <c r="BD17" s="6"/>
       <c r="BE17" s="6"/>
-      <c r="BF17" s="3"/>
-    </row>
-    <row r="18" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF17" s="6"/>
+      <c r="BG17" s="6"/>
+      <c r="BH17" s="6"/>
+      <c r="BI17" s="6"/>
+      <c r="BJ17" s="3"/>
+    </row>
+    <row r="18" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" ref="C18:H18" si="8">+C15-C16-C17</f>
+        <f t="shared" ref="C18:H18" si="9">+C15-C16-C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>66.891999999999541</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>109.63900000000015</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I18" s="6">
@@ -2020,59 +2152,65 @@
         <v>118.05799999999985</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" ref="J18:M18" si="9">+J15-J16-J17</f>
+        <f t="shared" ref="J18:O18" si="10">+J15-J16-J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>132.87200000000016</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>127.3240000000001</v>
       </c>
       <c r="M18" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>138.059</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6">
-        <f t="shared" ref="P18:W18" si="10">+P15-P16-P17</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="N18" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="R18" s="6">
+      <c r="O18" s="6">
         <f t="shared" si="10"/>
+        <v>142.66899999999964</v>
+      </c>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6">
+        <f t="shared" ref="T18:AA18" si="11">+T15-T16-T17</f>
         <v>0</v>
       </c>
-      <c r="S18" s="6">
-        <f t="shared" si="10"/>
+      <c r="U18" s="6">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="T18" s="6">
-        <f t="shared" si="10"/>
+      <c r="V18" s="6">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="U18" s="6">
-        <f t="shared" si="10"/>
+      <c r="W18" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="11"/>
         <v>465.77299999999985</v>
       </c>
-      <c r="V18" s="6">
-        <f t="shared" si="10"/>
+      <c r="Z18" s="6">
+        <f t="shared" si="11"/>
         <v>674.81400000000065</v>
       </c>
-      <c r="W18" s="6">
-        <f t="shared" si="10"/>
+      <c r="AA18" s="6">
+        <f t="shared" si="11"/>
         <v>816.11800000000085</v>
       </c>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
       <c r="AB18" s="6"/>
       <c r="AC18" s="6"/>
       <c r="AD18" s="6"/>
@@ -2103,9 +2241,13 @@
       <c r="BC18" s="6"/>
       <c r="BD18" s="6"/>
       <c r="BE18" s="6"/>
-      <c r="BF18" s="3"/>
-    </row>
-    <row r="19" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF18" s="6"/>
+      <c r="BG18" s="6"/>
+      <c r="BH18" s="6"/>
+      <c r="BI18" s="6"/>
+      <c r="BJ18" s="3"/>
+    </row>
+    <row r="19" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>35</v>
       </c>
@@ -2133,25 +2275,27 @@
         <v>33.308999999999997</v>
       </c>
       <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <v>27.925000000000001</v>
+      </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
-      <c r="U19" s="6">
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6">
         <v>126.124</v>
       </c>
-      <c r="V19" s="6">
+      <c r="Z19" s="6">
         <v>171.17500000000001</v>
       </c>
-      <c r="W19" s="6">
+      <c r="AA19" s="6">
         <v>205.965</v>
       </c>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
       <c r="AD19" s="6"/>
@@ -2182,34 +2326,38 @@
       <c r="BC19" s="6"/>
       <c r="BD19" s="6"/>
       <c r="BE19" s="6"/>
-      <c r="BF19" s="3"/>
-    </row>
-    <row r="20" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF19" s="6"/>
+      <c r="BG19" s="6"/>
+      <c r="BH19" s="6"/>
+      <c r="BI19" s="6"/>
+      <c r="BJ19" s="3"/>
+    </row>
+    <row r="20" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:H20" si="11">+C18-C19</f>
+        <f t="shared" ref="C20:H20" si="12">+C18-C19</f>
         <v>0</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>48.55099999999954</v>
       </c>
       <c r="F20" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>78.514000000000152</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I20" s="6">
@@ -2217,59 +2365,65 @@
         <v>90.616999999999848</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" ref="J20:M20" si="12">+J18-J19</f>
+        <f t="shared" ref="J20:O20" si="13">+J18-J19</f>
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100.83300000000015</v>
       </c>
       <c r="L20" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>94.185000000000088</v>
       </c>
       <c r="M20" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>104.75</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6">
-        <f t="shared" ref="P20:W20" si="13">+P18-P19</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
+      <c r="N20" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R20" s="6">
+      <c r="O20" s="6">
         <f t="shared" si="13"/>
+        <v>114.74399999999964</v>
+      </c>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6">
+        <f t="shared" ref="T20:AA20" si="14">+T18-T19</f>
         <v>0</v>
       </c>
-      <c r="S20" s="6">
-        <f t="shared" si="13"/>
+      <c r="U20" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T20" s="6">
-        <f t="shared" si="13"/>
+      <c r="V20" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U20" s="6">
-        <f t="shared" si="13"/>
+      <c r="W20" s="6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="6">
+        <f t="shared" si="14"/>
         <v>339.64899999999989</v>
       </c>
-      <c r="V20" s="6">
-        <f t="shared" si="13"/>
+      <c r="Z20" s="6">
+        <f t="shared" si="14"/>
         <v>503.63900000000064</v>
       </c>
-      <c r="W20" s="6">
-        <f t="shared" si="13"/>
+      <c r="AA20" s="6">
+        <f t="shared" si="14"/>
         <v>610.15300000000082</v>
       </c>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
       <c r="AC20" s="6"/>
       <c r="AD20" s="6"/>
@@ -2300,9 +2454,13 @@
       <c r="BC20" s="6"/>
       <c r="BD20" s="6"/>
       <c r="BE20" s="6"/>
-      <c r="BF20" s="3"/>
-    </row>
-    <row r="21" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF20" s="6"/>
+      <c r="BG20" s="6"/>
+      <c r="BH20" s="6"/>
+      <c r="BI20" s="6"/>
+      <c r="BJ20" s="3"/>
+    </row>
+    <row r="21" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -2358,34 +2516,38 @@
       <c r="BC21" s="6"/>
       <c r="BD21" s="6"/>
       <c r="BE21" s="6"/>
-      <c r="BF21" s="3"/>
-    </row>
-    <row r="22" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF21" s="6"/>
+      <c r="BG21" s="6"/>
+      <c r="BH21" s="6"/>
+      <c r="BI21" s="6"/>
+      <c r="BJ21" s="3"/>
+    </row>
+    <row r="22" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="6" t="e">
-        <f t="shared" ref="C22:H22" si="14">+C20/C23</f>
+        <f t="shared" ref="C22:H22" si="15">+C20/C23</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D22" s="6" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.75032067627922083</v>
       </c>
       <c r="F22" s="6" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.229258975121732</v>
       </c>
       <c r="H22" s="6" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I22" s="6">
@@ -2393,44 +2555,50 @@
         <v>1.4256249705017046</v>
       </c>
       <c r="J22" s="6" t="e">
-        <f t="shared" ref="J22:M22" si="15">+J20/J23</f>
+        <f t="shared" ref="J22:O22" si="16">+J20/J23</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.5982912756784198</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4741051445385267</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.6631736051570289</v>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="N22" s="6" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" si="16"/>
+        <v>1.8282982791586941</v>
+      </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="12">
-        <f t="shared" ref="U22:V22" si="16">+U20/U23</f>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="12">
+        <f t="shared" ref="Y22:Z22" si="17">+Y20/Y23</f>
         <v>5.2518709797130114</v>
       </c>
-      <c r="V22" s="12">
-        <f t="shared" si="16"/>
+      <c r="Z22" s="12">
+        <f t="shared" si="17"/>
         <v>7.9146211144985488</v>
       </c>
-      <c r="W22" s="12">
-        <f>+W20/W23</f>
+      <c r="AA22" s="12">
+        <f>+AA20/AA23</f>
         <v>9.6874285532833859</v>
       </c>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
       <c r="AD22" s="6"/>
@@ -2461,9 +2629,13 @@
       <c r="BC22" s="6"/>
       <c r="BD22" s="6"/>
       <c r="BE22" s="6"/>
-      <c r="BF22" s="3"/>
-    </row>
-    <row r="23" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF22" s="6"/>
+      <c r="BG22" s="6"/>
+      <c r="BH22" s="6"/>
+      <c r="BI22" s="6"/>
+      <c r="BJ22" s="3"/>
+    </row>
+    <row r="23" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
@@ -2491,25 +2663,27 @@
         <v>62.981999999999999</v>
       </c>
       <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="O23" s="6">
+        <v>62.76</v>
+      </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
-      <c r="U23" s="6">
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6">
         <v>64.671999999999997</v>
       </c>
-      <c r="V23" s="6">
+      <c r="Z23" s="6">
         <v>63.634</v>
       </c>
-      <c r="W23" s="6">
+      <c r="AA23" s="6">
         <v>62.984000000000002</v>
       </c>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
       <c r="AD23" s="6"/>
@@ -2540,9 +2714,13 @@
       <c r="BC23" s="6"/>
       <c r="BD23" s="6"/>
       <c r="BE23" s="6"/>
-      <c r="BF23" s="3"/>
-    </row>
-    <row r="24" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF23" s="6"/>
+      <c r="BG23" s="6"/>
+      <c r="BH23" s="6"/>
+      <c r="BI23" s="6"/>
+      <c r="BJ23" s="3"/>
+    </row>
+    <row r="24" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -2598,9 +2776,13 @@
       <c r="BC24" s="6"/>
       <c r="BD24" s="6"/>
       <c r="BE24" s="6"/>
-      <c r="BF24" s="3"/>
-    </row>
-    <row r="25" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF24" s="6"/>
+      <c r="BG24" s="6"/>
+      <c r="BH24" s="6"/>
+      <c r="BI24" s="6"/>
+      <c r="BJ24" s="3"/>
+    </row>
+    <row r="25" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>31</v>
       </c>
@@ -2609,11 +2791,11 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="8" t="e">
-        <f t="shared" ref="G25:H25" si="17">+G7/C7-1</f>
+        <f t="shared" ref="G25:H25" si="18">+G7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="8" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="8">
@@ -2636,11 +2818,17 @@
         <f>+M7/I7-1</f>
         <v>7.1025520252136154E-2</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
+      <c r="N25" s="8" t="e">
+        <f t="shared" ref="N25:O25" si="19">+N7/J7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="19"/>
+        <v>0.14075007388119887</v>
+      </c>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
@@ -2680,34 +2868,38 @@
       <c r="BC25" s="6"/>
       <c r="BD25" s="6"/>
       <c r="BE25" s="6"/>
-      <c r="BF25" s="3"/>
-    </row>
-    <row r="26" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF25" s="6"/>
+      <c r="BG25" s="6"/>
+      <c r="BH25" s="6"/>
+      <c r="BI25" s="6"/>
+      <c r="BJ25" s="3"/>
+    </row>
+    <row r="26" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:H26" si="18">+C10/C7</f>
+        <f t="shared" ref="C26:H26" si="20">+C10/C7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.3611607856566898</v>
       </c>
       <c r="F26" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.34944208323929205</v>
       </c>
       <c r="H26" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="9">
@@ -2730,11 +2922,17 @@
         <f>+M10/M7</f>
         <v>0.34958087985714498</v>
       </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="N26" s="9" t="e">
+        <f t="shared" ref="N26:O26" si="21">+N10/N7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="21"/>
+        <v>0.34636355966351373</v>
+      </c>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2774,34 +2972,38 @@
       <c r="BC26" s="6"/>
       <c r="BD26" s="6"/>
       <c r="BE26" s="6"/>
-      <c r="BF26" s="3"/>
-    </row>
-    <row r="27" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF26" s="6"/>
+      <c r="BG26" s="6"/>
+      <c r="BH26" s="6"/>
+      <c r="BI26" s="6"/>
+      <c r="BJ26" s="3"/>
+    </row>
+    <row r="27" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C27" s="9" t="e">
-        <f t="shared" ref="C27:H27" si="19">+C15/C7</f>
+        <f t="shared" ref="C27:H27" si="22">+C15/C7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.3768831797377741E-2</v>
       </c>
       <c r="F27" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.347667403611104E-2</v>
       </c>
       <c r="H27" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="9">
@@ -2824,11 +3026,17 @@
         <f>+M15/M7</f>
         <v>5.6193459364531219E-2</v>
       </c>
-      <c r="N27" s="9"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+      <c r="N27" s="9" t="e">
+        <f t="shared" ref="N27:O27" si="23">+N15/N7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="23"/>
+        <v>5.3563833008747418E-2</v>
+      </c>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -2868,34 +3076,38 @@
       <c r="BC27" s="6"/>
       <c r="BD27" s="6"/>
       <c r="BE27" s="6"/>
-      <c r="BF27" s="3"/>
-    </row>
-    <row r="28" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF27" s="6"/>
+      <c r="BG27" s="6"/>
+      <c r="BH27" s="6"/>
+      <c r="BI27" s="6"/>
+      <c r="BJ27" s="3"/>
+    </row>
+    <row r="28" spans="2:62" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="9" t="e">
-        <f t="shared" ref="C28:H28" si="20">+C19/C18</f>
+        <f t="shared" ref="C28:H28" si="24">+C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.27418824373617362</v>
       </c>
       <c r="F28" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.28388620837475675</v>
       </c>
       <c r="H28" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="9">
@@ -2918,11 +3130,17 @@
         <f>+M19/M18</f>
         <v>0.24126641508340635</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
+      <c r="N28" s="9" t="e">
+        <f t="shared" ref="N28:O28" si="25">+N19/N18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" si="25"/>
+        <v>0.19573278007135447</v>
+      </c>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
       <c r="S28" s="6"/>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -2962,9 +3180,13 @@
       <c r="BC28" s="6"/>
       <c r="BD28" s="6"/>
       <c r="BE28" s="6"/>
-      <c r="BF28" s="3"/>
-    </row>
-    <row r="29" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF28" s="6"/>
+      <c r="BG28" s="6"/>
+      <c r="BH28" s="6"/>
+      <c r="BI28" s="6"/>
+      <c r="BJ28" s="3"/>
+    </row>
+    <row r="29" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -3020,9 +3242,13 @@
       <c r="BC29" s="6"/>
       <c r="BD29" s="6"/>
       <c r="BE29" s="6"/>
-      <c r="BF29" s="3"/>
-    </row>
-    <row r="30" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF29" s="6"/>
+      <c r="BG29" s="6"/>
+      <c r="BH29" s="6"/>
+      <c r="BI29" s="6"/>
+      <c r="BJ29" s="3"/>
+    </row>
+    <row r="30" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -3078,9 +3304,13 @@
       <c r="BC30" s="6"/>
       <c r="BD30" s="6"/>
       <c r="BE30" s="6"/>
-      <c r="BF30" s="3"/>
-    </row>
-    <row r="31" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF30" s="6"/>
+      <c r="BG30" s="6"/>
+      <c r="BH30" s="6"/>
+      <c r="BI30" s="6"/>
+      <c r="BJ30" s="3"/>
+    </row>
+    <row r="31" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -3136,9 +3366,13 @@
       <c r="BC31" s="6"/>
       <c r="BD31" s="6"/>
       <c r="BE31" s="6"/>
-      <c r="BF31" s="3"/>
-    </row>
-    <row r="32" spans="2:58" x14ac:dyDescent="0.2">
+      <c r="BF31" s="6"/>
+      <c r="BG31" s="6"/>
+      <c r="BH31" s="6"/>
+      <c r="BI31" s="6"/>
+      <c r="BJ31" s="3"/>
+    </row>
+    <row r="32" spans="2:62" x14ac:dyDescent="0.2">
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -3194,9 +3428,13 @@
       <c r="BC32" s="6"/>
       <c r="BD32" s="6"/>
       <c r="BE32" s="6"/>
-      <c r="BF32" s="3"/>
-    </row>
-    <row r="33" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF32" s="6"/>
+      <c r="BG32" s="6"/>
+      <c r="BH32" s="6"/>
+      <c r="BI32" s="6"/>
+      <c r="BJ32" s="3"/>
+    </row>
+    <row r="33" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -3252,9 +3490,13 @@
       <c r="BC33" s="6"/>
       <c r="BD33" s="6"/>
       <c r="BE33" s="6"/>
-      <c r="BF33" s="3"/>
-    </row>
-    <row r="34" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF33" s="6"/>
+      <c r="BG33" s="6"/>
+      <c r="BH33" s="6"/>
+      <c r="BI33" s="6"/>
+      <c r="BJ33" s="3"/>
+    </row>
+    <row r="34" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3310,9 +3552,13 @@
       <c r="BC34" s="6"/>
       <c r="BD34" s="6"/>
       <c r="BE34" s="6"/>
-      <c r="BF34" s="3"/>
-    </row>
-    <row r="35" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF34" s="6"/>
+      <c r="BG34" s="6"/>
+      <c r="BH34" s="6"/>
+      <c r="BI34" s="6"/>
+      <c r="BJ34" s="3"/>
+    </row>
+    <row r="35" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -3368,9 +3614,13 @@
       <c r="BC35" s="6"/>
       <c r="BD35" s="6"/>
       <c r="BE35" s="6"/>
-      <c r="BF35" s="3"/>
-    </row>
-    <row r="36" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF35" s="6"/>
+      <c r="BG35" s="6"/>
+      <c r="BH35" s="6"/>
+      <c r="BI35" s="6"/>
+      <c r="BJ35" s="3"/>
+    </row>
+    <row r="36" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -3426,9 +3676,13 @@
       <c r="BC36" s="6"/>
       <c r="BD36" s="6"/>
       <c r="BE36" s="6"/>
-      <c r="BF36" s="3"/>
-    </row>
-    <row r="37" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF36" s="6"/>
+      <c r="BG36" s="6"/>
+      <c r="BH36" s="6"/>
+      <c r="BI36" s="6"/>
+      <c r="BJ36" s="3"/>
+    </row>
+    <row r="37" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -3484,9 +3738,13 @@
       <c r="BC37" s="6"/>
       <c r="BD37" s="6"/>
       <c r="BE37" s="6"/>
-      <c r="BF37" s="3"/>
-    </row>
-    <row r="38" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF37" s="6"/>
+      <c r="BG37" s="6"/>
+      <c r="BH37" s="6"/>
+      <c r="BI37" s="6"/>
+      <c r="BJ37" s="3"/>
+    </row>
+    <row r="38" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -3542,9 +3800,13 @@
       <c r="BC38" s="6"/>
       <c r="BD38" s="6"/>
       <c r="BE38" s="6"/>
-      <c r="BF38" s="3"/>
-    </row>
-    <row r="39" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF38" s="6"/>
+      <c r="BG38" s="6"/>
+      <c r="BH38" s="6"/>
+      <c r="BI38" s="6"/>
+      <c r="BJ38" s="3"/>
+    </row>
+    <row r="39" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -3600,9 +3862,13 @@
       <c r="BC39" s="6"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
-      <c r="BF39" s="3"/>
-    </row>
-    <row r="40" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF39" s="6"/>
+      <c r="BG39" s="6"/>
+      <c r="BH39" s="6"/>
+      <c r="BI39" s="6"/>
+      <c r="BJ39" s="3"/>
+    </row>
+    <row r="40" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -3658,9 +3924,13 @@
       <c r="BC40" s="6"/>
       <c r="BD40" s="6"/>
       <c r="BE40" s="6"/>
-      <c r="BF40" s="3"/>
-    </row>
-    <row r="41" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF40" s="6"/>
+      <c r="BG40" s="6"/>
+      <c r="BH40" s="6"/>
+      <c r="BI40" s="6"/>
+      <c r="BJ40" s="3"/>
+    </row>
+    <row r="41" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -3716,9 +3986,13 @@
       <c r="BC41" s="6"/>
       <c r="BD41" s="6"/>
       <c r="BE41" s="6"/>
-      <c r="BF41" s="3"/>
-    </row>
-    <row r="42" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF41" s="6"/>
+      <c r="BG41" s="6"/>
+      <c r="BH41" s="6"/>
+      <c r="BI41" s="6"/>
+      <c r="BJ41" s="3"/>
+    </row>
+    <row r="42" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -3774,9 +4048,13 @@
       <c r="BC42" s="6"/>
       <c r="BD42" s="6"/>
       <c r="BE42" s="6"/>
-      <c r="BF42" s="3"/>
-    </row>
-    <row r="43" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF42" s="6"/>
+      <c r="BG42" s="6"/>
+      <c r="BH42" s="6"/>
+      <c r="BI42" s="6"/>
+      <c r="BJ42" s="3"/>
+    </row>
+    <row r="43" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -3832,9 +4110,13 @@
       <c r="BC43" s="6"/>
       <c r="BD43" s="6"/>
       <c r="BE43" s="6"/>
-      <c r="BF43" s="3"/>
-    </row>
-    <row r="44" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF43" s="6"/>
+      <c r="BG43" s="6"/>
+      <c r="BH43" s="6"/>
+      <c r="BI43" s="6"/>
+      <c r="BJ43" s="3"/>
+    </row>
+    <row r="44" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -3890,9 +4172,13 @@
       <c r="BC44" s="6"/>
       <c r="BD44" s="6"/>
       <c r="BE44" s="6"/>
-      <c r="BF44" s="3"/>
-    </row>
-    <row r="45" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF44" s="6"/>
+      <c r="BG44" s="6"/>
+      <c r="BH44" s="6"/>
+      <c r="BI44" s="6"/>
+      <c r="BJ44" s="3"/>
+    </row>
+    <row r="45" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -3948,9 +4234,13 @@
       <c r="BC45" s="6"/>
       <c r="BD45" s="6"/>
       <c r="BE45" s="6"/>
-      <c r="BF45" s="3"/>
-    </row>
-    <row r="46" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF45" s="6"/>
+      <c r="BG45" s="6"/>
+      <c r="BH45" s="6"/>
+      <c r="BI45" s="6"/>
+      <c r="BJ45" s="3"/>
+    </row>
+    <row r="46" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -4006,9 +4296,13 @@
       <c r="BC46" s="6"/>
       <c r="BD46" s="6"/>
       <c r="BE46" s="6"/>
-      <c r="BF46" s="3"/>
-    </row>
-    <row r="47" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF46" s="6"/>
+      <c r="BG46" s="6"/>
+      <c r="BH46" s="6"/>
+      <c r="BI46" s="6"/>
+      <c r="BJ46" s="3"/>
+    </row>
+    <row r="47" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -4064,9 +4358,13 @@
       <c r="BC47" s="6"/>
       <c r="BD47" s="6"/>
       <c r="BE47" s="6"/>
-      <c r="BF47" s="3"/>
-    </row>
-    <row r="48" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF47" s="6"/>
+      <c r="BG47" s="6"/>
+      <c r="BH47" s="6"/>
+      <c r="BI47" s="6"/>
+      <c r="BJ47" s="3"/>
+    </row>
+    <row r="48" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -4122,9 +4420,13 @@
       <c r="BC48" s="6"/>
       <c r="BD48" s="6"/>
       <c r="BE48" s="6"/>
-      <c r="BF48" s="3"/>
-    </row>
-    <row r="49" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF48" s="6"/>
+      <c r="BG48" s="6"/>
+      <c r="BH48" s="6"/>
+      <c r="BI48" s="6"/>
+      <c r="BJ48" s="3"/>
+    </row>
+    <row r="49" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -4180,9 +4482,13 @@
       <c r="BC49" s="6"/>
       <c r="BD49" s="6"/>
       <c r="BE49" s="6"/>
-      <c r="BF49" s="3"/>
-    </row>
-    <row r="50" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF49" s="6"/>
+      <c r="BG49" s="6"/>
+      <c r="BH49" s="6"/>
+      <c r="BI49" s="6"/>
+      <c r="BJ49" s="3"/>
+    </row>
+    <row r="50" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -4238,9 +4544,13 @@
       <c r="BC50" s="6"/>
       <c r="BD50" s="6"/>
       <c r="BE50" s="6"/>
-      <c r="BF50" s="3"/>
-    </row>
-    <row r="51" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF50" s="6"/>
+      <c r="BG50" s="6"/>
+      <c r="BH50" s="6"/>
+      <c r="BI50" s="6"/>
+      <c r="BJ50" s="3"/>
+    </row>
+    <row r="51" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -4296,9 +4606,13 @@
       <c r="BC51" s="6"/>
       <c r="BD51" s="6"/>
       <c r="BE51" s="6"/>
-      <c r="BF51" s="3"/>
-    </row>
-    <row r="52" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF51" s="6"/>
+      <c r="BG51" s="6"/>
+      <c r="BH51" s="6"/>
+      <c r="BI51" s="6"/>
+      <c r="BJ51" s="3"/>
+    </row>
+    <row r="52" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -4354,9 +4668,13 @@
       <c r="BC52" s="6"/>
       <c r="BD52" s="6"/>
       <c r="BE52" s="6"/>
-      <c r="BF52" s="3"/>
-    </row>
-    <row r="53" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF52" s="6"/>
+      <c r="BG52" s="6"/>
+      <c r="BH52" s="6"/>
+      <c r="BI52" s="6"/>
+      <c r="BJ52" s="3"/>
+    </row>
+    <row r="53" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -4412,9 +4730,13 @@
       <c r="BC53" s="6"/>
       <c r="BD53" s="6"/>
       <c r="BE53" s="6"/>
-      <c r="BF53" s="3"/>
-    </row>
-    <row r="54" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF53" s="6"/>
+      <c r="BG53" s="6"/>
+      <c r="BH53" s="6"/>
+      <c r="BI53" s="6"/>
+      <c r="BJ53" s="3"/>
+    </row>
+    <row r="54" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -4470,9 +4792,13 @@
       <c r="BC54" s="6"/>
       <c r="BD54" s="6"/>
       <c r="BE54" s="6"/>
-      <c r="BF54" s="3"/>
-    </row>
-    <row r="55" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF54" s="6"/>
+      <c r="BG54" s="6"/>
+      <c r="BH54" s="6"/>
+      <c r="BI54" s="6"/>
+      <c r="BJ54" s="3"/>
+    </row>
+    <row r="55" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -4528,9 +4854,13 @@
       <c r="BC55" s="6"/>
       <c r="BD55" s="6"/>
       <c r="BE55" s="6"/>
-      <c r="BF55" s="3"/>
-    </row>
-    <row r="56" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF55" s="6"/>
+      <c r="BG55" s="6"/>
+      <c r="BH55" s="6"/>
+      <c r="BI55" s="6"/>
+      <c r="BJ55" s="3"/>
+    </row>
+    <row r="56" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -4586,9 +4916,13 @@
       <c r="BC56" s="6"/>
       <c r="BD56" s="6"/>
       <c r="BE56" s="6"/>
-      <c r="BF56" s="3"/>
-    </row>
-    <row r="57" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF56" s="6"/>
+      <c r="BG56" s="6"/>
+      <c r="BH56" s="6"/>
+      <c r="BI56" s="6"/>
+      <c r="BJ56" s="3"/>
+    </row>
+    <row r="57" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -4644,9 +4978,13 @@
       <c r="BC57" s="6"/>
       <c r="BD57" s="6"/>
       <c r="BE57" s="6"/>
-      <c r="BF57" s="3"/>
-    </row>
-    <row r="58" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF57" s="6"/>
+      <c r="BG57" s="6"/>
+      <c r="BH57" s="6"/>
+      <c r="BI57" s="6"/>
+      <c r="BJ57" s="3"/>
+    </row>
+    <row r="58" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -4702,9 +5040,13 @@
       <c r="BC58" s="6"/>
       <c r="BD58" s="6"/>
       <c r="BE58" s="6"/>
-      <c r="BF58" s="3"/>
-    </row>
-    <row r="59" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF58" s="6"/>
+      <c r="BG58" s="6"/>
+      <c r="BH58" s="6"/>
+      <c r="BI58" s="6"/>
+      <c r="BJ58" s="3"/>
+    </row>
+    <row r="59" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -4760,9 +5102,13 @@
       <c r="BC59" s="6"/>
       <c r="BD59" s="6"/>
       <c r="BE59" s="6"/>
-      <c r="BF59" s="3"/>
-    </row>
-    <row r="60" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF59" s="6"/>
+      <c r="BG59" s="6"/>
+      <c r="BH59" s="6"/>
+      <c r="BI59" s="6"/>
+      <c r="BJ59" s="3"/>
+    </row>
+    <row r="60" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -4818,9 +5164,13 @@
       <c r="BC60" s="6"/>
       <c r="BD60" s="6"/>
       <c r="BE60" s="6"/>
-      <c r="BF60" s="3"/>
-    </row>
-    <row r="61" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF60" s="6"/>
+      <c r="BG60" s="6"/>
+      <c r="BH60" s="6"/>
+      <c r="BI60" s="6"/>
+      <c r="BJ60" s="3"/>
+    </row>
+    <row r="61" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -4876,9 +5226,13 @@
       <c r="BC61" s="6"/>
       <c r="BD61" s="6"/>
       <c r="BE61" s="6"/>
-      <c r="BF61" s="3"/>
-    </row>
-    <row r="62" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF61" s="6"/>
+      <c r="BG61" s="6"/>
+      <c r="BH61" s="6"/>
+      <c r="BI61" s="6"/>
+      <c r="BJ61" s="3"/>
+    </row>
+    <row r="62" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -4934,9 +5288,13 @@
       <c r="BC62" s="6"/>
       <c r="BD62" s="6"/>
       <c r="BE62" s="6"/>
-      <c r="BF62" s="3"/>
-    </row>
-    <row r="63" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF62" s="6"/>
+      <c r="BG62" s="6"/>
+      <c r="BH62" s="6"/>
+      <c r="BI62" s="6"/>
+      <c r="BJ62" s="3"/>
+    </row>
+    <row r="63" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -4992,9 +5350,13 @@
       <c r="BC63" s="6"/>
       <c r="BD63" s="6"/>
       <c r="BE63" s="6"/>
-      <c r="BF63" s="3"/>
-    </row>
-    <row r="64" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF63" s="6"/>
+      <c r="BG63" s="6"/>
+      <c r="BH63" s="6"/>
+      <c r="BI63" s="6"/>
+      <c r="BJ63" s="3"/>
+    </row>
+    <row r="64" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -5050,9 +5412,13 @@
       <c r="BC64" s="6"/>
       <c r="BD64" s="6"/>
       <c r="BE64" s="6"/>
-      <c r="BF64" s="3"/>
-    </row>
-    <row r="65" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF64" s="6"/>
+      <c r="BG64" s="6"/>
+      <c r="BH64" s="6"/>
+      <c r="BI64" s="6"/>
+      <c r="BJ64" s="3"/>
+    </row>
+    <row r="65" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -5108,9 +5474,13 @@
       <c r="BC65" s="6"/>
       <c r="BD65" s="6"/>
       <c r="BE65" s="6"/>
-      <c r="BF65" s="3"/>
-    </row>
-    <row r="66" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF65" s="6"/>
+      <c r="BG65" s="6"/>
+      <c r="BH65" s="6"/>
+      <c r="BI65" s="6"/>
+      <c r="BJ65" s="3"/>
+    </row>
+    <row r="66" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -5166,9 +5536,13 @@
       <c r="BC66" s="6"/>
       <c r="BD66" s="6"/>
       <c r="BE66" s="6"/>
-      <c r="BF66" s="3"/>
-    </row>
-    <row r="67" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF66" s="6"/>
+      <c r="BG66" s="6"/>
+      <c r="BH66" s="6"/>
+      <c r="BI66" s="6"/>
+      <c r="BJ66" s="3"/>
+    </row>
+    <row r="67" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -5224,9 +5598,13 @@
       <c r="BC67" s="6"/>
       <c r="BD67" s="6"/>
       <c r="BE67" s="6"/>
-      <c r="BF67" s="3"/>
-    </row>
-    <row r="68" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF67" s="6"/>
+      <c r="BG67" s="6"/>
+      <c r="BH67" s="6"/>
+      <c r="BI67" s="6"/>
+      <c r="BJ67" s="3"/>
+    </row>
+    <row r="68" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -5282,9 +5660,13 @@
       <c r="BC68" s="6"/>
       <c r="BD68" s="6"/>
       <c r="BE68" s="6"/>
-      <c r="BF68" s="3"/>
-    </row>
-    <row r="69" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF68" s="6"/>
+      <c r="BG68" s="6"/>
+      <c r="BH68" s="6"/>
+      <c r="BI68" s="6"/>
+      <c r="BJ68" s="3"/>
+    </row>
+    <row r="69" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -5340,9 +5722,13 @@
       <c r="BC69" s="6"/>
       <c r="BD69" s="6"/>
       <c r="BE69" s="6"/>
-      <c r="BF69" s="3"/>
-    </row>
-    <row r="70" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF69" s="6"/>
+      <c r="BG69" s="6"/>
+      <c r="BH69" s="6"/>
+      <c r="BI69" s="6"/>
+      <c r="BJ69" s="3"/>
+    </row>
+    <row r="70" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -5398,9 +5784,13 @@
       <c r="BC70" s="6"/>
       <c r="BD70" s="6"/>
       <c r="BE70" s="6"/>
-      <c r="BF70" s="3"/>
-    </row>
-    <row r="71" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF70" s="6"/>
+      <c r="BG70" s="6"/>
+      <c r="BH70" s="6"/>
+      <c r="BI70" s="6"/>
+      <c r="BJ70" s="3"/>
+    </row>
+    <row r="71" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -5456,9 +5846,13 @@
       <c r="BC71" s="6"/>
       <c r="BD71" s="6"/>
       <c r="BE71" s="6"/>
-      <c r="BF71" s="3"/>
-    </row>
-    <row r="72" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF71" s="6"/>
+      <c r="BG71" s="6"/>
+      <c r="BH71" s="6"/>
+      <c r="BI71" s="6"/>
+      <c r="BJ71" s="3"/>
+    </row>
+    <row r="72" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -5514,9 +5908,13 @@
       <c r="BC72" s="6"/>
       <c r="BD72" s="6"/>
       <c r="BE72" s="6"/>
-      <c r="BF72" s="3"/>
-    </row>
-    <row r="73" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF72" s="6"/>
+      <c r="BG72" s="6"/>
+      <c r="BH72" s="6"/>
+      <c r="BI72" s="6"/>
+      <c r="BJ72" s="3"/>
+    </row>
+    <row r="73" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -5572,9 +5970,13 @@
       <c r="BC73" s="6"/>
       <c r="BD73" s="6"/>
       <c r="BE73" s="6"/>
-      <c r="BF73" s="3"/>
-    </row>
-    <row r="74" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF73" s="6"/>
+      <c r="BG73" s="6"/>
+      <c r="BH73" s="6"/>
+      <c r="BI73" s="6"/>
+      <c r="BJ73" s="3"/>
+    </row>
+    <row r="74" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -5630,9 +6032,13 @@
       <c r="BC74" s="6"/>
       <c r="BD74" s="6"/>
       <c r="BE74" s="6"/>
-      <c r="BF74" s="3"/>
-    </row>
-    <row r="75" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF74" s="6"/>
+      <c r="BG74" s="6"/>
+      <c r="BH74" s="6"/>
+      <c r="BI74" s="6"/>
+      <c r="BJ74" s="3"/>
+    </row>
+    <row r="75" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -5688,9 +6094,13 @@
       <c r="BC75" s="6"/>
       <c r="BD75" s="6"/>
       <c r="BE75" s="6"/>
-      <c r="BF75" s="3"/>
-    </row>
-    <row r="76" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF75" s="6"/>
+      <c r="BG75" s="6"/>
+      <c r="BH75" s="6"/>
+      <c r="BI75" s="6"/>
+      <c r="BJ75" s="3"/>
+    </row>
+    <row r="76" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -5746,9 +6156,13 @@
       <c r="BC76" s="6"/>
       <c r="BD76" s="6"/>
       <c r="BE76" s="6"/>
-      <c r="BF76" s="3"/>
-    </row>
-    <row r="77" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF76" s="6"/>
+      <c r="BG76" s="6"/>
+      <c r="BH76" s="6"/>
+      <c r="BI76" s="6"/>
+      <c r="BJ76" s="3"/>
+    </row>
+    <row r="77" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -5804,9 +6218,13 @@
       <c r="BC77" s="6"/>
       <c r="BD77" s="6"/>
       <c r="BE77" s="6"/>
-      <c r="BF77" s="3"/>
-    </row>
-    <row r="78" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF77" s="6"/>
+      <c r="BG77" s="6"/>
+      <c r="BH77" s="6"/>
+      <c r="BI77" s="6"/>
+      <c r="BJ77" s="3"/>
+    </row>
+    <row r="78" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -5862,9 +6280,13 @@
       <c r="BC78" s="6"/>
       <c r="BD78" s="6"/>
       <c r="BE78" s="6"/>
-      <c r="BF78" s="3"/>
-    </row>
-    <row r="79" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF78" s="6"/>
+      <c r="BG78" s="6"/>
+      <c r="BH78" s="6"/>
+      <c r="BI78" s="6"/>
+      <c r="BJ78" s="3"/>
+    </row>
+    <row r="79" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -5920,9 +6342,13 @@
       <c r="BC79" s="6"/>
       <c r="BD79" s="6"/>
       <c r="BE79" s="6"/>
-      <c r="BF79" s="3"/>
-    </row>
-    <row r="80" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF79" s="6"/>
+      <c r="BG79" s="6"/>
+      <c r="BH79" s="6"/>
+      <c r="BI79" s="6"/>
+      <c r="BJ79" s="3"/>
+    </row>
+    <row r="80" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -5978,9 +6404,13 @@
       <c r="BC80" s="6"/>
       <c r="BD80" s="6"/>
       <c r="BE80" s="6"/>
-      <c r="BF80" s="3"/>
-    </row>
-    <row r="81" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF80" s="6"/>
+      <c r="BG80" s="6"/>
+      <c r="BH80" s="6"/>
+      <c r="BI80" s="6"/>
+      <c r="BJ80" s="3"/>
+    </row>
+    <row r="81" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -6036,9 +6466,13 @@
       <c r="BC81" s="6"/>
       <c r="BD81" s="6"/>
       <c r="BE81" s="6"/>
-      <c r="BF81" s="3"/>
-    </row>
-    <row r="82" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF81" s="6"/>
+      <c r="BG81" s="6"/>
+      <c r="BH81" s="6"/>
+      <c r="BI81" s="6"/>
+      <c r="BJ81" s="3"/>
+    </row>
+    <row r="82" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -6094,9 +6528,13 @@
       <c r="BC82" s="6"/>
       <c r="BD82" s="6"/>
       <c r="BE82" s="6"/>
-      <c r="BF82" s="3"/>
-    </row>
-    <row r="83" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF82" s="6"/>
+      <c r="BG82" s="6"/>
+      <c r="BH82" s="6"/>
+      <c r="BI82" s="6"/>
+      <c r="BJ82" s="3"/>
+    </row>
+    <row r="83" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -6152,9 +6590,13 @@
       <c r="BC83" s="6"/>
       <c r="BD83" s="6"/>
       <c r="BE83" s="6"/>
-      <c r="BF83" s="3"/>
-    </row>
-    <row r="84" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF83" s="6"/>
+      <c r="BG83" s="6"/>
+      <c r="BH83" s="6"/>
+      <c r="BI83" s="6"/>
+      <c r="BJ83" s="3"/>
+    </row>
+    <row r="84" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -6210,9 +6652,13 @@
       <c r="BC84" s="6"/>
       <c r="BD84" s="6"/>
       <c r="BE84" s="6"/>
-      <c r="BF84" s="3"/>
-    </row>
-    <row r="85" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF84" s="6"/>
+      <c r="BG84" s="6"/>
+      <c r="BH84" s="6"/>
+      <c r="BI84" s="6"/>
+      <c r="BJ84" s="3"/>
+    </row>
+    <row r="85" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -6268,9 +6714,13 @@
       <c r="BC85" s="6"/>
       <c r="BD85" s="6"/>
       <c r="BE85" s="6"/>
-      <c r="BF85" s="3"/>
-    </row>
-    <row r="86" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF85" s="6"/>
+      <c r="BG85" s="6"/>
+      <c r="BH85" s="6"/>
+      <c r="BI85" s="6"/>
+      <c r="BJ85" s="3"/>
+    </row>
+    <row r="86" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -6326,9 +6776,13 @@
       <c r="BC86" s="6"/>
       <c r="BD86" s="6"/>
       <c r="BE86" s="6"/>
-      <c r="BF86" s="3"/>
-    </row>
-    <row r="87" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF86" s="6"/>
+      <c r="BG86" s="6"/>
+      <c r="BH86" s="6"/>
+      <c r="BI86" s="6"/>
+      <c r="BJ86" s="3"/>
+    </row>
+    <row r="87" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
@@ -6384,9 +6838,13 @@
       <c r="BC87" s="6"/>
       <c r="BD87" s="6"/>
       <c r="BE87" s="6"/>
-      <c r="BF87" s="3"/>
-    </row>
-    <row r="88" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF87" s="6"/>
+      <c r="BG87" s="6"/>
+      <c r="BH87" s="6"/>
+      <c r="BI87" s="6"/>
+      <c r="BJ87" s="3"/>
+    </row>
+    <row r="88" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -6442,9 +6900,13 @@
       <c r="BC88" s="6"/>
       <c r="BD88" s="6"/>
       <c r="BE88" s="6"/>
-      <c r="BF88" s="3"/>
-    </row>
-    <row r="89" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF88" s="6"/>
+      <c r="BG88" s="6"/>
+      <c r="BH88" s="6"/>
+      <c r="BI88" s="6"/>
+      <c r="BJ88" s="3"/>
+    </row>
+    <row r="89" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -6500,9 +6962,13 @@
       <c r="BC89" s="6"/>
       <c r="BD89" s="6"/>
       <c r="BE89" s="6"/>
-      <c r="BF89" s="3"/>
-    </row>
-    <row r="90" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF89" s="6"/>
+      <c r="BG89" s="6"/>
+      <c r="BH89" s="6"/>
+      <c r="BI89" s="6"/>
+      <c r="BJ89" s="3"/>
+    </row>
+    <row r="90" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -6558,9 +7024,13 @@
       <c r="BC90" s="6"/>
       <c r="BD90" s="6"/>
       <c r="BE90" s="6"/>
-      <c r="BF90" s="3"/>
-    </row>
-    <row r="91" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF90" s="6"/>
+      <c r="BG90" s="6"/>
+      <c r="BH90" s="6"/>
+      <c r="BI90" s="6"/>
+      <c r="BJ90" s="3"/>
+    </row>
+    <row r="91" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -6616,9 +7086,13 @@
       <c r="BC91" s="6"/>
       <c r="BD91" s="6"/>
       <c r="BE91" s="6"/>
-      <c r="BF91" s="3"/>
-    </row>
-    <row r="92" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF91" s="6"/>
+      <c r="BG91" s="6"/>
+      <c r="BH91" s="6"/>
+      <c r="BI91" s="6"/>
+      <c r="BJ91" s="3"/>
+    </row>
+    <row r="92" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
@@ -6674,9 +7148,13 @@
       <c r="BC92" s="6"/>
       <c r="BD92" s="6"/>
       <c r="BE92" s="6"/>
-      <c r="BF92" s="3"/>
-    </row>
-    <row r="93" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF92" s="6"/>
+      <c r="BG92" s="6"/>
+      <c r="BH92" s="6"/>
+      <c r="BI92" s="6"/>
+      <c r="BJ92" s="3"/>
+    </row>
+    <row r="93" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -6732,9 +7210,13 @@
       <c r="BC93" s="6"/>
       <c r="BD93" s="6"/>
       <c r="BE93" s="6"/>
-      <c r="BF93" s="3"/>
-    </row>
-    <row r="94" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF93" s="6"/>
+      <c r="BG93" s="6"/>
+      <c r="BH93" s="6"/>
+      <c r="BI93" s="6"/>
+      <c r="BJ93" s="3"/>
+    </row>
+    <row r="94" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -6790,9 +7272,13 @@
       <c r="BC94" s="6"/>
       <c r="BD94" s="6"/>
       <c r="BE94" s="6"/>
-      <c r="BF94" s="3"/>
-    </row>
-    <row r="95" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF94" s="6"/>
+      <c r="BG94" s="6"/>
+      <c r="BH94" s="6"/>
+      <c r="BI94" s="6"/>
+      <c r="BJ94" s="3"/>
+    </row>
+    <row r="95" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -6848,9 +7334,13 @@
       <c r="BC95" s="6"/>
       <c r="BD95" s="6"/>
       <c r="BE95" s="6"/>
-      <c r="BF95" s="3"/>
-    </row>
-    <row r="96" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF95" s="6"/>
+      <c r="BG95" s="6"/>
+      <c r="BH95" s="6"/>
+      <c r="BI95" s="6"/>
+      <c r="BJ95" s="3"/>
+    </row>
+    <row r="96" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -6906,9 +7396,13 @@
       <c r="BC96" s="6"/>
       <c r="BD96" s="6"/>
       <c r="BE96" s="6"/>
-      <c r="BF96" s="3"/>
-    </row>
-    <row r="97" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF96" s="6"/>
+      <c r="BG96" s="6"/>
+      <c r="BH96" s="6"/>
+      <c r="BI96" s="6"/>
+      <c r="BJ96" s="3"/>
+    </row>
+    <row r="97" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -6964,9 +7458,13 @@
       <c r="BC97" s="6"/>
       <c r="BD97" s="6"/>
       <c r="BE97" s="6"/>
-      <c r="BF97" s="3"/>
-    </row>
-    <row r="98" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF97" s="6"/>
+      <c r="BG97" s="6"/>
+      <c r="BH97" s="6"/>
+      <c r="BI97" s="6"/>
+      <c r="BJ97" s="3"/>
+    </row>
+    <row r="98" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -7022,9 +7520,13 @@
       <c r="BC98" s="6"/>
       <c r="BD98" s="6"/>
       <c r="BE98" s="6"/>
-      <c r="BF98" s="3"/>
-    </row>
-    <row r="99" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF98" s="6"/>
+      <c r="BG98" s="6"/>
+      <c r="BH98" s="6"/>
+      <c r="BI98" s="6"/>
+      <c r="BJ98" s="3"/>
+    </row>
+    <row r="99" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -7080,9 +7582,13 @@
       <c r="BC99" s="6"/>
       <c r="BD99" s="6"/>
       <c r="BE99" s="6"/>
-      <c r="BF99" s="3"/>
-    </row>
-    <row r="100" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF99" s="6"/>
+      <c r="BG99" s="6"/>
+      <c r="BH99" s="6"/>
+      <c r="BI99" s="6"/>
+      <c r="BJ99" s="3"/>
+    </row>
+    <row r="100" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -7138,9 +7644,13 @@
       <c r="BC100" s="6"/>
       <c r="BD100" s="6"/>
       <c r="BE100" s="6"/>
-      <c r="BF100" s="3"/>
-    </row>
-    <row r="101" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF100" s="6"/>
+      <c r="BG100" s="6"/>
+      <c r="BH100" s="6"/>
+      <c r="BI100" s="6"/>
+      <c r="BJ100" s="3"/>
+    </row>
+    <row r="101" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -7196,9 +7706,13 @@
       <c r="BC101" s="6"/>
       <c r="BD101" s="6"/>
       <c r="BE101" s="6"/>
-      <c r="BF101" s="3"/>
-    </row>
-    <row r="102" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF101" s="6"/>
+      <c r="BG101" s="6"/>
+      <c r="BH101" s="6"/>
+      <c r="BI101" s="6"/>
+      <c r="BJ101" s="3"/>
+    </row>
+    <row r="102" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -7254,9 +7768,13 @@
       <c r="BC102" s="6"/>
       <c r="BD102" s="6"/>
       <c r="BE102" s="6"/>
-      <c r="BF102" s="3"/>
-    </row>
-    <row r="103" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF102" s="6"/>
+      <c r="BG102" s="6"/>
+      <c r="BH102" s="6"/>
+      <c r="BI102" s="6"/>
+      <c r="BJ102" s="3"/>
+    </row>
+    <row r="103" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -7312,9 +7830,13 @@
       <c r="BC103" s="6"/>
       <c r="BD103" s="6"/>
       <c r="BE103" s="6"/>
-      <c r="BF103" s="3"/>
-    </row>
-    <row r="104" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF103" s="6"/>
+      <c r="BG103" s="6"/>
+      <c r="BH103" s="6"/>
+      <c r="BI103" s="6"/>
+      <c r="BJ103" s="3"/>
+    </row>
+    <row r="104" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -7370,9 +7892,13 @@
       <c r="BC104" s="6"/>
       <c r="BD104" s="6"/>
       <c r="BE104" s="6"/>
-      <c r="BF104" s="3"/>
-    </row>
-    <row r="105" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF104" s="6"/>
+      <c r="BG104" s="6"/>
+      <c r="BH104" s="6"/>
+      <c r="BI104" s="6"/>
+      <c r="BJ104" s="3"/>
+    </row>
+    <row r="105" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
@@ -7428,9 +7954,13 @@
       <c r="BC105" s="6"/>
       <c r="BD105" s="6"/>
       <c r="BE105" s="6"/>
-      <c r="BF105" s="3"/>
-    </row>
-    <row r="106" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF105" s="6"/>
+      <c r="BG105" s="6"/>
+      <c r="BH105" s="6"/>
+      <c r="BI105" s="6"/>
+      <c r="BJ105" s="3"/>
+    </row>
+    <row r="106" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -7486,9 +8016,13 @@
       <c r="BC106" s="6"/>
       <c r="BD106" s="6"/>
       <c r="BE106" s="6"/>
-      <c r="BF106" s="3"/>
-    </row>
-    <row r="107" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF106" s="6"/>
+      <c r="BG106" s="6"/>
+      <c r="BH106" s="6"/>
+      <c r="BI106" s="6"/>
+      <c r="BJ106" s="3"/>
+    </row>
+    <row r="107" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
@@ -7544,9 +8078,13 @@
       <c r="BC107" s="6"/>
       <c r="BD107" s="6"/>
       <c r="BE107" s="6"/>
-      <c r="BF107" s="3"/>
-    </row>
-    <row r="108" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF107" s="6"/>
+      <c r="BG107" s="6"/>
+      <c r="BH107" s="6"/>
+      <c r="BI107" s="6"/>
+      <c r="BJ107" s="3"/>
+    </row>
+    <row r="108" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -7602,9 +8140,13 @@
       <c r="BC108" s="6"/>
       <c r="BD108" s="6"/>
       <c r="BE108" s="6"/>
-      <c r="BF108" s="3"/>
-    </row>
-    <row r="109" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF108" s="6"/>
+      <c r="BG108" s="6"/>
+      <c r="BH108" s="6"/>
+      <c r="BI108" s="6"/>
+      <c r="BJ108" s="3"/>
+    </row>
+    <row r="109" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
@@ -7660,9 +8202,13 @@
       <c r="BC109" s="6"/>
       <c r="BD109" s="6"/>
       <c r="BE109" s="6"/>
-      <c r="BF109" s="3"/>
-    </row>
-    <row r="110" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF109" s="6"/>
+      <c r="BG109" s="6"/>
+      <c r="BH109" s="6"/>
+      <c r="BI109" s="6"/>
+      <c r="BJ109" s="3"/>
+    </row>
+    <row r="110" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -7718,9 +8264,13 @@
       <c r="BC110" s="6"/>
       <c r="BD110" s="6"/>
       <c r="BE110" s="6"/>
-      <c r="BF110" s="3"/>
-    </row>
-    <row r="111" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF110" s="6"/>
+      <c r="BG110" s="6"/>
+      <c r="BH110" s="6"/>
+      <c r="BI110" s="6"/>
+      <c r="BJ110" s="3"/>
+    </row>
+    <row r="111" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
@@ -7776,9 +8326,13 @@
       <c r="BC111" s="6"/>
       <c r="BD111" s="6"/>
       <c r="BE111" s="6"/>
-      <c r="BF111" s="3"/>
-    </row>
-    <row r="112" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF111" s="6"/>
+      <c r="BG111" s="6"/>
+      <c r="BH111" s="6"/>
+      <c r="BI111" s="6"/>
+      <c r="BJ111" s="3"/>
+    </row>
+    <row r="112" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -7834,9 +8388,13 @@
       <c r="BC112" s="6"/>
       <c r="BD112" s="6"/>
       <c r="BE112" s="6"/>
-      <c r="BF112" s="3"/>
-    </row>
-    <row r="113" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF112" s="6"/>
+      <c r="BG112" s="6"/>
+      <c r="BH112" s="6"/>
+      <c r="BI112" s="6"/>
+      <c r="BJ112" s="3"/>
+    </row>
+    <row r="113" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -7892,9 +8450,13 @@
       <c r="BC113" s="6"/>
       <c r="BD113" s="6"/>
       <c r="BE113" s="6"/>
-      <c r="BF113" s="3"/>
-    </row>
-    <row r="114" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF113" s="6"/>
+      <c r="BG113" s="6"/>
+      <c r="BH113" s="6"/>
+      <c r="BI113" s="6"/>
+      <c r="BJ113" s="3"/>
+    </row>
+    <row r="114" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -7950,9 +8512,13 @@
       <c r="BC114" s="6"/>
       <c r="BD114" s="6"/>
       <c r="BE114" s="6"/>
-      <c r="BF114" s="3"/>
-    </row>
-    <row r="115" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF114" s="6"/>
+      <c r="BG114" s="6"/>
+      <c r="BH114" s="6"/>
+      <c r="BI114" s="6"/>
+      <c r="BJ114" s="3"/>
+    </row>
+    <row r="115" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -8008,9 +8574,13 @@
       <c r="BC115" s="6"/>
       <c r="BD115" s="6"/>
       <c r="BE115" s="6"/>
-      <c r="BF115" s="3"/>
-    </row>
-    <row r="116" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF115" s="6"/>
+      <c r="BG115" s="6"/>
+      <c r="BH115" s="6"/>
+      <c r="BI115" s="6"/>
+      <c r="BJ115" s="3"/>
+    </row>
+    <row r="116" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
@@ -8066,9 +8636,13 @@
       <c r="BC116" s="6"/>
       <c r="BD116" s="6"/>
       <c r="BE116" s="6"/>
-      <c r="BF116" s="3"/>
-    </row>
-    <row r="117" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF116" s="6"/>
+      <c r="BG116" s="6"/>
+      <c r="BH116" s="6"/>
+      <c r="BI116" s="6"/>
+      <c r="BJ116" s="3"/>
+    </row>
+    <row r="117" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -8124,9 +8698,13 @@
       <c r="BC117" s="6"/>
       <c r="BD117" s="6"/>
       <c r="BE117" s="6"/>
-      <c r="BF117" s="3"/>
-    </row>
-    <row r="118" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF117" s="6"/>
+      <c r="BG117" s="6"/>
+      <c r="BH117" s="6"/>
+      <c r="BI117" s="6"/>
+      <c r="BJ117" s="3"/>
+    </row>
+    <row r="118" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
@@ -8182,9 +8760,13 @@
       <c r="BC118" s="6"/>
       <c r="BD118" s="6"/>
       <c r="BE118" s="6"/>
-      <c r="BF118" s="3"/>
-    </row>
-    <row r="119" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF118" s="6"/>
+      <c r="BG118" s="6"/>
+      <c r="BH118" s="6"/>
+      <c r="BI118" s="6"/>
+      <c r="BJ118" s="3"/>
+    </row>
+    <row r="119" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -8240,9 +8822,13 @@
       <c r="BC119" s="6"/>
       <c r="BD119" s="6"/>
       <c r="BE119" s="6"/>
-      <c r="BF119" s="3"/>
-    </row>
-    <row r="120" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF119" s="6"/>
+      <c r="BG119" s="6"/>
+      <c r="BH119" s="6"/>
+      <c r="BI119" s="6"/>
+      <c r="BJ119" s="3"/>
+    </row>
+    <row r="120" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -8298,9 +8884,13 @@
       <c r="BC120" s="6"/>
       <c r="BD120" s="6"/>
       <c r="BE120" s="6"/>
-      <c r="BF120" s="3"/>
-    </row>
-    <row r="121" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF120" s="6"/>
+      <c r="BG120" s="6"/>
+      <c r="BH120" s="6"/>
+      <c r="BI120" s="6"/>
+      <c r="BJ120" s="3"/>
+    </row>
+    <row r="121" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -8356,9 +8946,13 @@
       <c r="BC121" s="6"/>
       <c r="BD121" s="6"/>
       <c r="BE121" s="6"/>
-      <c r="BF121" s="3"/>
-    </row>
-    <row r="122" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF121" s="6"/>
+      <c r="BG121" s="6"/>
+      <c r="BH121" s="6"/>
+      <c r="BI121" s="6"/>
+      <c r="BJ121" s="3"/>
+    </row>
+    <row r="122" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -8414,9 +9008,13 @@
       <c r="BC122" s="6"/>
       <c r="BD122" s="6"/>
       <c r="BE122" s="6"/>
-      <c r="BF122" s="3"/>
-    </row>
-    <row r="123" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF122" s="6"/>
+      <c r="BG122" s="6"/>
+      <c r="BH122" s="6"/>
+      <c r="BI122" s="6"/>
+      <c r="BJ122" s="3"/>
+    </row>
+    <row r="123" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
@@ -8472,9 +9070,13 @@
       <c r="BC123" s="6"/>
       <c r="BD123" s="6"/>
       <c r="BE123" s="6"/>
-      <c r="BF123" s="3"/>
-    </row>
-    <row r="124" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF123" s="6"/>
+      <c r="BG123" s="6"/>
+      <c r="BH123" s="6"/>
+      <c r="BI123" s="6"/>
+      <c r="BJ123" s="3"/>
+    </row>
+    <row r="124" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -8530,9 +9132,13 @@
       <c r="BC124" s="6"/>
       <c r="BD124" s="6"/>
       <c r="BE124" s="6"/>
-      <c r="BF124" s="3"/>
-    </row>
-    <row r="125" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF124" s="6"/>
+      <c r="BG124" s="6"/>
+      <c r="BH124" s="6"/>
+      <c r="BI124" s="6"/>
+      <c r="BJ124" s="3"/>
+    </row>
+    <row r="125" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
@@ -8588,9 +9194,13 @@
       <c r="BC125" s="6"/>
       <c r="BD125" s="6"/>
       <c r="BE125" s="6"/>
-      <c r="BF125" s="3"/>
-    </row>
-    <row r="126" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF125" s="6"/>
+      <c r="BG125" s="6"/>
+      <c r="BH125" s="6"/>
+      <c r="BI125" s="6"/>
+      <c r="BJ125" s="3"/>
+    </row>
+    <row r="126" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
@@ -8646,9 +9256,13 @@
       <c r="BC126" s="6"/>
       <c r="BD126" s="6"/>
       <c r="BE126" s="6"/>
-      <c r="BF126" s="3"/>
-    </row>
-    <row r="127" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF126" s="6"/>
+      <c r="BG126" s="6"/>
+      <c r="BH126" s="6"/>
+      <c r="BI126" s="6"/>
+      <c r="BJ126" s="3"/>
+    </row>
+    <row r="127" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
@@ -8704,9 +9318,13 @@
       <c r="BC127" s="6"/>
       <c r="BD127" s="6"/>
       <c r="BE127" s="6"/>
-      <c r="BF127" s="3"/>
-    </row>
-    <row r="128" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF127" s="6"/>
+      <c r="BG127" s="6"/>
+      <c r="BH127" s="6"/>
+      <c r="BI127" s="6"/>
+      <c r="BJ127" s="3"/>
+    </row>
+    <row r="128" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C128" s="6"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -8762,9 +9380,13 @@
       <c r="BC128" s="6"/>
       <c r="BD128" s="6"/>
       <c r="BE128" s="6"/>
-      <c r="BF128" s="3"/>
-    </row>
-    <row r="129" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF128" s="6"/>
+      <c r="BG128" s="6"/>
+      <c r="BH128" s="6"/>
+      <c r="BI128" s="6"/>
+      <c r="BJ128" s="3"/>
+    </row>
+    <row r="129" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
@@ -8820,9 +9442,13 @@
       <c r="BC129" s="6"/>
       <c r="BD129" s="6"/>
       <c r="BE129" s="6"/>
-      <c r="BF129" s="3"/>
-    </row>
-    <row r="130" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF129" s="6"/>
+      <c r="BG129" s="6"/>
+      <c r="BH129" s="6"/>
+      <c r="BI129" s="6"/>
+      <c r="BJ129" s="3"/>
+    </row>
+    <row r="130" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -8878,9 +9504,13 @@
       <c r="BC130" s="6"/>
       <c r="BD130" s="6"/>
       <c r="BE130" s="6"/>
-      <c r="BF130" s="3"/>
-    </row>
-    <row r="131" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF130" s="6"/>
+      <c r="BG130" s="6"/>
+      <c r="BH130" s="6"/>
+      <c r="BI130" s="6"/>
+      <c r="BJ130" s="3"/>
+    </row>
+    <row r="131" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C131" s="6"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
@@ -8936,9 +9566,13 @@
       <c r="BC131" s="6"/>
       <c r="BD131" s="6"/>
       <c r="BE131" s="6"/>
-      <c r="BF131" s="3"/>
-    </row>
-    <row r="132" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF131" s="6"/>
+      <c r="BG131" s="6"/>
+      <c r="BH131" s="6"/>
+      <c r="BI131" s="6"/>
+      <c r="BJ131" s="3"/>
+    </row>
+    <row r="132" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
@@ -8994,9 +9628,13 @@
       <c r="BC132" s="6"/>
       <c r="BD132" s="6"/>
       <c r="BE132" s="6"/>
-      <c r="BF132" s="3"/>
-    </row>
-    <row r="133" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF132" s="6"/>
+      <c r="BG132" s="6"/>
+      <c r="BH132" s="6"/>
+      <c r="BI132" s="6"/>
+      <c r="BJ132" s="3"/>
+    </row>
+    <row r="133" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
@@ -9052,9 +9690,13 @@
       <c r="BC133" s="6"/>
       <c r="BD133" s="6"/>
       <c r="BE133" s="6"/>
-      <c r="BF133" s="3"/>
-    </row>
-    <row r="134" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF133" s="6"/>
+      <c r="BG133" s="6"/>
+      <c r="BH133" s="6"/>
+      <c r="BI133" s="6"/>
+      <c r="BJ133" s="3"/>
+    </row>
+    <row r="134" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
@@ -9110,9 +9752,13 @@
       <c r="BC134" s="6"/>
       <c r="BD134" s="6"/>
       <c r="BE134" s="6"/>
-      <c r="BF134" s="3"/>
-    </row>
-    <row r="135" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF134" s="6"/>
+      <c r="BG134" s="6"/>
+      <c r="BH134" s="6"/>
+      <c r="BI134" s="6"/>
+      <c r="BJ134" s="3"/>
+    </row>
+    <row r="135" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
@@ -9168,9 +9814,13 @@
       <c r="BC135" s="6"/>
       <c r="BD135" s="6"/>
       <c r="BE135" s="6"/>
-      <c r="BF135" s="3"/>
-    </row>
-    <row r="136" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF135" s="6"/>
+      <c r="BG135" s="6"/>
+      <c r="BH135" s="6"/>
+      <c r="BI135" s="6"/>
+      <c r="BJ135" s="3"/>
+    </row>
+    <row r="136" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
@@ -9226,9 +9876,13 @@
       <c r="BC136" s="6"/>
       <c r="BD136" s="6"/>
       <c r="BE136" s="6"/>
-      <c r="BF136" s="3"/>
-    </row>
-    <row r="137" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF136" s="6"/>
+      <c r="BG136" s="6"/>
+      <c r="BH136" s="6"/>
+      <c r="BI136" s="6"/>
+      <c r="BJ136" s="3"/>
+    </row>
+    <row r="137" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
@@ -9284,9 +9938,13 @@
       <c r="BC137" s="6"/>
       <c r="BD137" s="6"/>
       <c r="BE137" s="6"/>
-      <c r="BF137" s="3"/>
-    </row>
-    <row r="138" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF137" s="6"/>
+      <c r="BG137" s="6"/>
+      <c r="BH137" s="6"/>
+      <c r="BI137" s="6"/>
+      <c r="BJ137" s="3"/>
+    </row>
+    <row r="138" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C138" s="6"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -9342,9 +10000,13 @@
       <c r="BC138" s="6"/>
       <c r="BD138" s="6"/>
       <c r="BE138" s="6"/>
-      <c r="BF138" s="3"/>
-    </row>
-    <row r="139" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF138" s="6"/>
+      <c r="BG138" s="6"/>
+      <c r="BH138" s="6"/>
+      <c r="BI138" s="6"/>
+      <c r="BJ138" s="3"/>
+    </row>
+    <row r="139" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
@@ -9400,9 +10062,13 @@
       <c r="BC139" s="6"/>
       <c r="BD139" s="6"/>
       <c r="BE139" s="6"/>
-      <c r="BF139" s="3"/>
-    </row>
-    <row r="140" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF139" s="6"/>
+      <c r="BG139" s="6"/>
+      <c r="BH139" s="6"/>
+      <c r="BI139" s="6"/>
+      <c r="BJ139" s="3"/>
+    </row>
+    <row r="140" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C140" s="6"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
@@ -9458,9 +10124,13 @@
       <c r="BC140" s="6"/>
       <c r="BD140" s="6"/>
       <c r="BE140" s="6"/>
-      <c r="BF140" s="3"/>
-    </row>
-    <row r="141" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF140" s="6"/>
+      <c r="BG140" s="6"/>
+      <c r="BH140" s="6"/>
+      <c r="BI140" s="6"/>
+      <c r="BJ140" s="3"/>
+    </row>
+    <row r="141" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -9516,9 +10186,13 @@
       <c r="BC141" s="6"/>
       <c r="BD141" s="6"/>
       <c r="BE141" s="6"/>
-      <c r="BF141" s="3"/>
-    </row>
-    <row r="142" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF141" s="6"/>
+      <c r="BG141" s="6"/>
+      <c r="BH141" s="6"/>
+      <c r="BI141" s="6"/>
+      <c r="BJ141" s="3"/>
+    </row>
+    <row r="142" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C142" s="6"/>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
@@ -9574,9 +10248,13 @@
       <c r="BC142" s="6"/>
       <c r="BD142" s="6"/>
       <c r="BE142" s="6"/>
-      <c r="BF142" s="3"/>
-    </row>
-    <row r="143" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF142" s="6"/>
+      <c r="BG142" s="6"/>
+      <c r="BH142" s="6"/>
+      <c r="BI142" s="6"/>
+      <c r="BJ142" s="3"/>
+    </row>
+    <row r="143" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -9632,9 +10310,13 @@
       <c r="BC143" s="6"/>
       <c r="BD143" s="6"/>
       <c r="BE143" s="6"/>
-      <c r="BF143" s="3"/>
-    </row>
-    <row r="144" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF143" s="6"/>
+      <c r="BG143" s="6"/>
+      <c r="BH143" s="6"/>
+      <c r="BI143" s="6"/>
+      <c r="BJ143" s="3"/>
+    </row>
+    <row r="144" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
@@ -9690,9 +10372,13 @@
       <c r="BC144" s="6"/>
       <c r="BD144" s="6"/>
       <c r="BE144" s="6"/>
-      <c r="BF144" s="3"/>
-    </row>
-    <row r="145" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF144" s="6"/>
+      <c r="BG144" s="6"/>
+      <c r="BH144" s="6"/>
+      <c r="BI144" s="6"/>
+      <c r="BJ144" s="3"/>
+    </row>
+    <row r="145" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C145" s="6"/>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
@@ -9748,9 +10434,13 @@
       <c r="BC145" s="6"/>
       <c r="BD145" s="6"/>
       <c r="BE145" s="6"/>
-      <c r="BF145" s="3"/>
-    </row>
-    <row r="146" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF145" s="6"/>
+      <c r="BG145" s="6"/>
+      <c r="BH145" s="6"/>
+      <c r="BI145" s="6"/>
+      <c r="BJ145" s="3"/>
+    </row>
+    <row r="146" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
@@ -9806,9 +10496,13 @@
       <c r="BC146" s="6"/>
       <c r="BD146" s="6"/>
       <c r="BE146" s="6"/>
-      <c r="BF146" s="3"/>
-    </row>
-    <row r="147" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF146" s="6"/>
+      <c r="BG146" s="6"/>
+      <c r="BH146" s="6"/>
+      <c r="BI146" s="6"/>
+      <c r="BJ146" s="3"/>
+    </row>
+    <row r="147" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C147" s="6"/>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -9864,9 +10558,13 @@
       <c r="BC147" s="6"/>
       <c r="BD147" s="6"/>
       <c r="BE147" s="6"/>
-      <c r="BF147" s="3"/>
-    </row>
-    <row r="148" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF147" s="6"/>
+      <c r="BG147" s="6"/>
+      <c r="BH147" s="6"/>
+      <c r="BI147" s="6"/>
+      <c r="BJ147" s="3"/>
+    </row>
+    <row r="148" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C148" s="6"/>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
@@ -9922,9 +10620,13 @@
       <c r="BC148" s="6"/>
       <c r="BD148" s="6"/>
       <c r="BE148" s="6"/>
-      <c r="BF148" s="3"/>
-    </row>
-    <row r="149" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF148" s="6"/>
+      <c r="BG148" s="6"/>
+      <c r="BH148" s="6"/>
+      <c r="BI148" s="6"/>
+      <c r="BJ148" s="3"/>
+    </row>
+    <row r="149" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
@@ -9980,9 +10682,13 @@
       <c r="BC149" s="6"/>
       <c r="BD149" s="6"/>
       <c r="BE149" s="6"/>
-      <c r="BF149" s="3"/>
-    </row>
-    <row r="150" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF149" s="6"/>
+      <c r="BG149" s="6"/>
+      <c r="BH149" s="6"/>
+      <c r="BI149" s="6"/>
+      <c r="BJ149" s="3"/>
+    </row>
+    <row r="150" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
@@ -10038,9 +10744,13 @@
       <c r="BC150" s="6"/>
       <c r="BD150" s="6"/>
       <c r="BE150" s="6"/>
-      <c r="BF150" s="3"/>
-    </row>
-    <row r="151" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF150" s="6"/>
+      <c r="BG150" s="6"/>
+      <c r="BH150" s="6"/>
+      <c r="BI150" s="6"/>
+      <c r="BJ150" s="3"/>
+    </row>
+    <row r="151" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
@@ -10096,9 +10806,13 @@
       <c r="BC151" s="6"/>
       <c r="BD151" s="6"/>
       <c r="BE151" s="6"/>
-      <c r="BF151" s="3"/>
-    </row>
-    <row r="152" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF151" s="6"/>
+      <c r="BG151" s="6"/>
+      <c r="BH151" s="6"/>
+      <c r="BI151" s="6"/>
+      <c r="BJ151" s="3"/>
+    </row>
+    <row r="152" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
@@ -10154,9 +10868,13 @@
       <c r="BC152" s="6"/>
       <c r="BD152" s="6"/>
       <c r="BE152" s="6"/>
-      <c r="BF152" s="3"/>
-    </row>
-    <row r="153" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF152" s="6"/>
+      <c r="BG152" s="6"/>
+      <c r="BH152" s="6"/>
+      <c r="BI152" s="6"/>
+      <c r="BJ152" s="3"/>
+    </row>
+    <row r="153" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
@@ -10212,9 +10930,13 @@
       <c r="BC153" s="6"/>
       <c r="BD153" s="6"/>
       <c r="BE153" s="6"/>
-      <c r="BF153" s="3"/>
-    </row>
-    <row r="154" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF153" s="6"/>
+      <c r="BG153" s="6"/>
+      <c r="BH153" s="6"/>
+      <c r="BI153" s="6"/>
+      <c r="BJ153" s="3"/>
+    </row>
+    <row r="154" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
@@ -10270,9 +10992,13 @@
       <c r="BC154" s="6"/>
       <c r="BD154" s="6"/>
       <c r="BE154" s="6"/>
-      <c r="BF154" s="3"/>
-    </row>
-    <row r="155" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF154" s="6"/>
+      <c r="BG154" s="6"/>
+      <c r="BH154" s="6"/>
+      <c r="BI154" s="6"/>
+      <c r="BJ154" s="3"/>
+    </row>
+    <row r="155" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
@@ -10328,9 +11054,13 @@
       <c r="BC155" s="6"/>
       <c r="BD155" s="6"/>
       <c r="BE155" s="6"/>
-      <c r="BF155" s="3"/>
-    </row>
-    <row r="156" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF155" s="6"/>
+      <c r="BG155" s="6"/>
+      <c r="BH155" s="6"/>
+      <c r="BI155" s="6"/>
+      <c r="BJ155" s="3"/>
+    </row>
+    <row r="156" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
@@ -10386,9 +11116,13 @@
       <c r="BC156" s="6"/>
       <c r="BD156" s="6"/>
       <c r="BE156" s="6"/>
-      <c r="BF156" s="3"/>
-    </row>
-    <row r="157" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF156" s="6"/>
+      <c r="BG156" s="6"/>
+      <c r="BH156" s="6"/>
+      <c r="BI156" s="6"/>
+      <c r="BJ156" s="3"/>
+    </row>
+    <row r="157" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
@@ -10444,9 +11178,13 @@
       <c r="BC157" s="6"/>
       <c r="BD157" s="6"/>
       <c r="BE157" s="6"/>
-      <c r="BF157" s="3"/>
-    </row>
-    <row r="158" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF157" s="6"/>
+      <c r="BG157" s="6"/>
+      <c r="BH157" s="6"/>
+      <c r="BI157" s="6"/>
+      <c r="BJ157" s="3"/>
+    </row>
+    <row r="158" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
@@ -10502,9 +11240,13 @@
       <c r="BC158" s="6"/>
       <c r="BD158" s="6"/>
       <c r="BE158" s="6"/>
-      <c r="BF158" s="3"/>
-    </row>
-    <row r="159" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF158" s="6"/>
+      <c r="BG158" s="6"/>
+      <c r="BH158" s="6"/>
+      <c r="BI158" s="6"/>
+      <c r="BJ158" s="3"/>
+    </row>
+    <row r="159" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
@@ -10560,9 +11302,13 @@
       <c r="BC159" s="6"/>
       <c r="BD159" s="6"/>
       <c r="BE159" s="6"/>
-      <c r="BF159" s="3"/>
-    </row>
-    <row r="160" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF159" s="6"/>
+      <c r="BG159" s="6"/>
+      <c r="BH159" s="6"/>
+      <c r="BI159" s="6"/>
+      <c r="BJ159" s="3"/>
+    </row>
+    <row r="160" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C160" s="6"/>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
@@ -10618,9 +11364,13 @@
       <c r="BC160" s="6"/>
       <c r="BD160" s="6"/>
       <c r="BE160" s="6"/>
-      <c r="BF160" s="3"/>
-    </row>
-    <row r="161" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF160" s="6"/>
+      <c r="BG160" s="6"/>
+      <c r="BH160" s="6"/>
+      <c r="BI160" s="6"/>
+      <c r="BJ160" s="3"/>
+    </row>
+    <row r="161" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C161" s="6"/>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
@@ -10676,9 +11426,13 @@
       <c r="BC161" s="6"/>
       <c r="BD161" s="6"/>
       <c r="BE161" s="6"/>
-      <c r="BF161" s="3"/>
-    </row>
-    <row r="162" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF161" s="6"/>
+      <c r="BG161" s="6"/>
+      <c r="BH161" s="6"/>
+      <c r="BI161" s="6"/>
+      <c r="BJ161" s="3"/>
+    </row>
+    <row r="162" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C162" s="6"/>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
@@ -10734,9 +11488,13 @@
       <c r="BC162" s="6"/>
       <c r="BD162" s="6"/>
       <c r="BE162" s="6"/>
-      <c r="BF162" s="3"/>
-    </row>
-    <row r="163" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF162" s="6"/>
+      <c r="BG162" s="6"/>
+      <c r="BH162" s="6"/>
+      <c r="BI162" s="6"/>
+      <c r="BJ162" s="3"/>
+    </row>
+    <row r="163" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
@@ -10792,9 +11550,13 @@
       <c r="BC163" s="6"/>
       <c r="BD163" s="6"/>
       <c r="BE163" s="6"/>
-      <c r="BF163" s="3"/>
-    </row>
-    <row r="164" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF163" s="6"/>
+      <c r="BG163" s="6"/>
+      <c r="BH163" s="6"/>
+      <c r="BI163" s="6"/>
+      <c r="BJ163" s="3"/>
+    </row>
+    <row r="164" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
@@ -10850,9 +11612,13 @@
       <c r="BC164" s="6"/>
       <c r="BD164" s="6"/>
       <c r="BE164" s="6"/>
-      <c r="BF164" s="3"/>
-    </row>
-    <row r="165" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF164" s="6"/>
+      <c r="BG164" s="6"/>
+      <c r="BH164" s="6"/>
+      <c r="BI164" s="6"/>
+      <c r="BJ164" s="3"/>
+    </row>
+    <row r="165" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
@@ -10908,9 +11674,13 @@
       <c r="BC165" s="6"/>
       <c r="BD165" s="6"/>
       <c r="BE165" s="6"/>
-      <c r="BF165" s="3"/>
-    </row>
-    <row r="166" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF165" s="6"/>
+      <c r="BG165" s="6"/>
+      <c r="BH165" s="6"/>
+      <c r="BI165" s="6"/>
+      <c r="BJ165" s="3"/>
+    </row>
+    <row r="166" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
@@ -10966,9 +11736,13 @@
       <c r="BC166" s="6"/>
       <c r="BD166" s="6"/>
       <c r="BE166" s="6"/>
-      <c r="BF166" s="3"/>
-    </row>
-    <row r="167" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF166" s="6"/>
+      <c r="BG166" s="6"/>
+      <c r="BH166" s="6"/>
+      <c r="BI166" s="6"/>
+      <c r="BJ166" s="3"/>
+    </row>
+    <row r="167" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
@@ -11024,9 +11798,13 @@
       <c r="BC167" s="6"/>
       <c r="BD167" s="6"/>
       <c r="BE167" s="6"/>
-      <c r="BF167" s="3"/>
-    </row>
-    <row r="168" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF167" s="6"/>
+      <c r="BG167" s="6"/>
+      <c r="BH167" s="6"/>
+      <c r="BI167" s="6"/>
+      <c r="BJ167" s="3"/>
+    </row>
+    <row r="168" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
@@ -11082,9 +11860,13 @@
       <c r="BC168" s="6"/>
       <c r="BD168" s="6"/>
       <c r="BE168" s="6"/>
-      <c r="BF168" s="3"/>
-    </row>
-    <row r="169" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF168" s="6"/>
+      <c r="BG168" s="6"/>
+      <c r="BH168" s="6"/>
+      <c r="BI168" s="6"/>
+      <c r="BJ168" s="3"/>
+    </row>
+    <row r="169" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
@@ -11140,9 +11922,13 @@
       <c r="BC169" s="6"/>
       <c r="BD169" s="6"/>
       <c r="BE169" s="6"/>
-      <c r="BF169" s="3"/>
-    </row>
-    <row r="170" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF169" s="6"/>
+      <c r="BG169" s="6"/>
+      <c r="BH169" s="6"/>
+      <c r="BI169" s="6"/>
+      <c r="BJ169" s="3"/>
+    </row>
+    <row r="170" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C170" s="6"/>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
@@ -11198,9 +11984,13 @@
       <c r="BC170" s="6"/>
       <c r="BD170" s="6"/>
       <c r="BE170" s="6"/>
-      <c r="BF170" s="3"/>
-    </row>
-    <row r="171" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF170" s="6"/>
+      <c r="BG170" s="6"/>
+      <c r="BH170" s="6"/>
+      <c r="BI170" s="6"/>
+      <c r="BJ170" s="3"/>
+    </row>
+    <row r="171" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C171" s="6"/>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
@@ -11256,9 +12046,13 @@
       <c r="BC171" s="6"/>
       <c r="BD171" s="6"/>
       <c r="BE171" s="6"/>
-      <c r="BF171" s="3"/>
-    </row>
-    <row r="172" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF171" s="6"/>
+      <c r="BG171" s="6"/>
+      <c r="BH171" s="6"/>
+      <c r="BI171" s="6"/>
+      <c r="BJ171" s="3"/>
+    </row>
+    <row r="172" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C172" s="6"/>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
@@ -11314,9 +12108,13 @@
       <c r="BC172" s="6"/>
       <c r="BD172" s="6"/>
       <c r="BE172" s="6"/>
-      <c r="BF172" s="3"/>
-    </row>
-    <row r="173" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF172" s="6"/>
+      <c r="BG172" s="6"/>
+      <c r="BH172" s="6"/>
+      <c r="BI172" s="6"/>
+      <c r="BJ172" s="3"/>
+    </row>
+    <row r="173" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
@@ -11372,9 +12170,13 @@
       <c r="BC173" s="6"/>
       <c r="BD173" s="6"/>
       <c r="BE173" s="6"/>
-      <c r="BF173" s="3"/>
-    </row>
-    <row r="174" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF173" s="6"/>
+      <c r="BG173" s="6"/>
+      <c r="BH173" s="6"/>
+      <c r="BI173" s="6"/>
+      <c r="BJ173" s="3"/>
+    </row>
+    <row r="174" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
@@ -11430,9 +12232,13 @@
       <c r="BC174" s="6"/>
       <c r="BD174" s="6"/>
       <c r="BE174" s="6"/>
-      <c r="BF174" s="3"/>
-    </row>
-    <row r="175" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF174" s="6"/>
+      <c r="BG174" s="6"/>
+      <c r="BH174" s="6"/>
+      <c r="BI174" s="6"/>
+      <c r="BJ174" s="3"/>
+    </row>
+    <row r="175" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
@@ -11488,9 +12294,13 @@
       <c r="BC175" s="6"/>
       <c r="BD175" s="6"/>
       <c r="BE175" s="6"/>
-      <c r="BF175" s="3"/>
-    </row>
-    <row r="176" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF175" s="6"/>
+      <c r="BG175" s="6"/>
+      <c r="BH175" s="6"/>
+      <c r="BI175" s="6"/>
+      <c r="BJ175" s="3"/>
+    </row>
+    <row r="176" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
@@ -11546,9 +12356,13 @@
       <c r="BC176" s="6"/>
       <c r="BD176" s="6"/>
       <c r="BE176" s="6"/>
-      <c r="BF176" s="3"/>
-    </row>
-    <row r="177" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF176" s="6"/>
+      <c r="BG176" s="6"/>
+      <c r="BH176" s="6"/>
+      <c r="BI176" s="6"/>
+      <c r="BJ176" s="3"/>
+    </row>
+    <row r="177" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
@@ -11604,9 +12418,13 @@
       <c r="BC177" s="6"/>
       <c r="BD177" s="6"/>
       <c r="BE177" s="6"/>
-      <c r="BF177" s="3"/>
-    </row>
-    <row r="178" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BF177" s="6"/>
+      <c r="BG177" s="6"/>
+      <c r="BH177" s="6"/>
+      <c r="BI177" s="6"/>
+      <c r="BJ177" s="3"/>
+    </row>
+    <row r="178" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -11663,8 +12481,12 @@
       <c r="BD178" s="3"/>
       <c r="BE178" s="3"/>
       <c r="BF178" s="3"/>
-    </row>
-    <row r="179" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG178" s="3"/>
+      <c r="BH178" s="3"/>
+      <c r="BI178" s="3"/>
+      <c r="BJ178" s="3"/>
+    </row>
+    <row r="179" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -11721,8 +12543,12 @@
       <c r="BD179" s="3"/>
       <c r="BE179" s="3"/>
       <c r="BF179" s="3"/>
-    </row>
-    <row r="180" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG179" s="3"/>
+      <c r="BH179" s="3"/>
+      <c r="BI179" s="3"/>
+      <c r="BJ179" s="3"/>
+    </row>
+    <row r="180" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -11779,8 +12605,12 @@
       <c r="BD180" s="3"/>
       <c r="BE180" s="3"/>
       <c r="BF180" s="3"/>
-    </row>
-    <row r="181" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG180" s="3"/>
+      <c r="BH180" s="3"/>
+      <c r="BI180" s="3"/>
+      <c r="BJ180" s="3"/>
+    </row>
+    <row r="181" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -11837,8 +12667,12 @@
       <c r="BD181" s="3"/>
       <c r="BE181" s="3"/>
       <c r="BF181" s="3"/>
-    </row>
-    <row r="182" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG181" s="3"/>
+      <c r="BH181" s="3"/>
+      <c r="BI181" s="3"/>
+      <c r="BJ181" s="3"/>
+    </row>
+    <row r="182" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -11895,8 +12729,12 @@
       <c r="BD182" s="3"/>
       <c r="BE182" s="3"/>
       <c r="BF182" s="3"/>
-    </row>
-    <row r="183" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG182" s="3"/>
+      <c r="BH182" s="3"/>
+      <c r="BI182" s="3"/>
+      <c r="BJ182" s="3"/>
+    </row>
+    <row r="183" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -11953,8 +12791,12 @@
       <c r="BD183" s="3"/>
       <c r="BE183" s="3"/>
       <c r="BF183" s="3"/>
-    </row>
-    <row r="184" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG183" s="3"/>
+      <c r="BH183" s="3"/>
+      <c r="BI183" s="3"/>
+      <c r="BJ183" s="3"/>
+    </row>
+    <row r="184" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -12011,8 +12853,12 @@
       <c r="BD184" s="3"/>
       <c r="BE184" s="3"/>
       <c r="BF184" s="3"/>
-    </row>
-    <row r="185" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG184" s="3"/>
+      <c r="BH184" s="3"/>
+      <c r="BI184" s="3"/>
+      <c r="BJ184" s="3"/>
+    </row>
+    <row r="185" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -12069,8 +12915,12 @@
       <c r="BD185" s="3"/>
       <c r="BE185" s="3"/>
       <c r="BF185" s="3"/>
-    </row>
-    <row r="186" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG185" s="3"/>
+      <c r="BH185" s="3"/>
+      <c r="BI185" s="3"/>
+      <c r="BJ185" s="3"/>
+    </row>
+    <row r="186" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -12127,8 +12977,12 @@
       <c r="BD186" s="3"/>
       <c r="BE186" s="3"/>
       <c r="BF186" s="3"/>
-    </row>
-    <row r="187" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG186" s="3"/>
+      <c r="BH186" s="3"/>
+      <c r="BI186" s="3"/>
+      <c r="BJ186" s="3"/>
+    </row>
+    <row r="187" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -12185,8 +13039,12 @@
       <c r="BD187" s="3"/>
       <c r="BE187" s="3"/>
       <c r="BF187" s="3"/>
-    </row>
-    <row r="188" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG187" s="3"/>
+      <c r="BH187" s="3"/>
+      <c r="BI187" s="3"/>
+      <c r="BJ187" s="3"/>
+    </row>
+    <row r="188" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -12243,8 +13101,12 @@
       <c r="BD188" s="3"/>
       <c r="BE188" s="3"/>
       <c r="BF188" s="3"/>
-    </row>
-    <row r="189" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG188" s="3"/>
+      <c r="BH188" s="3"/>
+      <c r="BI188" s="3"/>
+      <c r="BJ188" s="3"/>
+    </row>
+    <row r="189" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -12301,8 +13163,12 @@
       <c r="BD189" s="3"/>
       <c r="BE189" s="3"/>
       <c r="BF189" s="3"/>
-    </row>
-    <row r="190" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG189" s="3"/>
+      <c r="BH189" s="3"/>
+      <c r="BI189" s="3"/>
+      <c r="BJ189" s="3"/>
+    </row>
+    <row r="190" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -12359,8 +13225,12 @@
       <c r="BD190" s="3"/>
       <c r="BE190" s="3"/>
       <c r="BF190" s="3"/>
-    </row>
-    <row r="191" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG190" s="3"/>
+      <c r="BH190" s="3"/>
+      <c r="BI190" s="3"/>
+      <c r="BJ190" s="3"/>
+    </row>
+    <row r="191" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -12417,8 +13287,12 @@
       <c r="BD191" s="3"/>
       <c r="BE191" s="3"/>
       <c r="BF191" s="3"/>
-    </row>
-    <row r="192" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG191" s="3"/>
+      <c r="BH191" s="3"/>
+      <c r="BI191" s="3"/>
+      <c r="BJ191" s="3"/>
+    </row>
+    <row r="192" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -12475,8 +13349,12 @@
       <c r="BD192" s="3"/>
       <c r="BE192" s="3"/>
       <c r="BF192" s="3"/>
-    </row>
-    <row r="193" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG192" s="3"/>
+      <c r="BH192" s="3"/>
+      <c r="BI192" s="3"/>
+      <c r="BJ192" s="3"/>
+    </row>
+    <row r="193" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -12533,8 +13411,12 @@
       <c r="BD193" s="3"/>
       <c r="BE193" s="3"/>
       <c r="BF193" s="3"/>
-    </row>
-    <row r="194" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG193" s="3"/>
+      <c r="BH193" s="3"/>
+      <c r="BI193" s="3"/>
+      <c r="BJ193" s="3"/>
+    </row>
+    <row r="194" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -12591,8 +13473,12 @@
       <c r="BD194" s="3"/>
       <c r="BE194" s="3"/>
       <c r="BF194" s="3"/>
-    </row>
-    <row r="195" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG194" s="3"/>
+      <c r="BH194" s="3"/>
+      <c r="BI194" s="3"/>
+      <c r="BJ194" s="3"/>
+    </row>
+    <row r="195" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -12649,8 +13535,12 @@
       <c r="BD195" s="3"/>
       <c r="BE195" s="3"/>
       <c r="BF195" s="3"/>
-    </row>
-    <row r="196" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG195" s="3"/>
+      <c r="BH195" s="3"/>
+      <c r="BI195" s="3"/>
+      <c r="BJ195" s="3"/>
+    </row>
+    <row r="196" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -12707,8 +13597,12 @@
       <c r="BD196" s="3"/>
       <c r="BE196" s="3"/>
       <c r="BF196" s="3"/>
-    </row>
-    <row r="197" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG196" s="3"/>
+      <c r="BH196" s="3"/>
+      <c r="BI196" s="3"/>
+      <c r="BJ196" s="3"/>
+    </row>
+    <row r="197" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -12765,8 +13659,12 @@
       <c r="BD197" s="3"/>
       <c r="BE197" s="3"/>
       <c r="BF197" s="3"/>
-    </row>
-    <row r="198" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG197" s="3"/>
+      <c r="BH197" s="3"/>
+      <c r="BI197" s="3"/>
+      <c r="BJ197" s="3"/>
+    </row>
+    <row r="198" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -12823,8 +13721,12 @@
       <c r="BD198" s="3"/>
       <c r="BE198" s="3"/>
       <c r="BF198" s="3"/>
-    </row>
-    <row r="199" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG198" s="3"/>
+      <c r="BH198" s="3"/>
+      <c r="BI198" s="3"/>
+      <c r="BJ198" s="3"/>
+    </row>
+    <row r="199" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -12881,8 +13783,12 @@
       <c r="BD199" s="3"/>
       <c r="BE199" s="3"/>
       <c r="BF199" s="3"/>
-    </row>
-    <row r="200" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG199" s="3"/>
+      <c r="BH199" s="3"/>
+      <c r="BI199" s="3"/>
+      <c r="BJ199" s="3"/>
+    </row>
+    <row r="200" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -12939,8 +13845,12 @@
       <c r="BD200" s="3"/>
       <c r="BE200" s="3"/>
       <c r="BF200" s="3"/>
-    </row>
-    <row r="201" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG200" s="3"/>
+      <c r="BH200" s="3"/>
+      <c r="BI200" s="3"/>
+      <c r="BJ200" s="3"/>
+    </row>
+    <row r="201" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -12997,8 +13907,12 @@
       <c r="BD201" s="3"/>
       <c r="BE201" s="3"/>
       <c r="BF201" s="3"/>
-    </row>
-    <row r="202" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG201" s="3"/>
+      <c r="BH201" s="3"/>
+      <c r="BI201" s="3"/>
+      <c r="BJ201" s="3"/>
+    </row>
+    <row r="202" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -13055,8 +13969,12 @@
       <c r="BD202" s="3"/>
       <c r="BE202" s="3"/>
       <c r="BF202" s="3"/>
-    </row>
-    <row r="203" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG202" s="3"/>
+      <c r="BH202" s="3"/>
+      <c r="BI202" s="3"/>
+      <c r="BJ202" s="3"/>
+    </row>
+    <row r="203" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -13113,8 +14031,12 @@
       <c r="BD203" s="3"/>
       <c r="BE203" s="3"/>
       <c r="BF203" s="3"/>
-    </row>
-    <row r="204" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG203" s="3"/>
+      <c r="BH203" s="3"/>
+      <c r="BI203" s="3"/>
+      <c r="BJ203" s="3"/>
+    </row>
+    <row r="204" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -13171,8 +14093,12 @@
       <c r="BD204" s="3"/>
       <c r="BE204" s="3"/>
       <c r="BF204" s="3"/>
-    </row>
-    <row r="205" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG204" s="3"/>
+      <c r="BH204" s="3"/>
+      <c r="BI204" s="3"/>
+      <c r="BJ204" s="3"/>
+    </row>
+    <row r="205" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -13229,8 +14155,12 @@
       <c r="BD205" s="3"/>
       <c r="BE205" s="3"/>
       <c r="BF205" s="3"/>
-    </row>
-    <row r="206" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG205" s="3"/>
+      <c r="BH205" s="3"/>
+      <c r="BI205" s="3"/>
+      <c r="BJ205" s="3"/>
+    </row>
+    <row r="206" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -13287,8 +14217,12 @@
       <c r="BD206" s="3"/>
       <c r="BE206" s="3"/>
       <c r="BF206" s="3"/>
-    </row>
-    <row r="207" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG206" s="3"/>
+      <c r="BH206" s="3"/>
+      <c r="BI206" s="3"/>
+      <c r="BJ206" s="3"/>
+    </row>
+    <row r="207" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -13345,8 +14279,12 @@
       <c r="BD207" s="3"/>
       <c r="BE207" s="3"/>
       <c r="BF207" s="3"/>
-    </row>
-    <row r="208" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG207" s="3"/>
+      <c r="BH207" s="3"/>
+      <c r="BI207" s="3"/>
+      <c r="BJ207" s="3"/>
+    </row>
+    <row r="208" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -13403,8 +14341,12 @@
       <c r="BD208" s="3"/>
       <c r="BE208" s="3"/>
       <c r="BF208" s="3"/>
-    </row>
-    <row r="209" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG208" s="3"/>
+      <c r="BH208" s="3"/>
+      <c r="BI208" s="3"/>
+      <c r="BJ208" s="3"/>
+    </row>
+    <row r="209" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -13461,8 +14403,12 @@
       <c r="BD209" s="3"/>
       <c r="BE209" s="3"/>
       <c r="BF209" s="3"/>
-    </row>
-    <row r="210" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG209" s="3"/>
+      <c r="BH209" s="3"/>
+      <c r="BI209" s="3"/>
+      <c r="BJ209" s="3"/>
+    </row>
+    <row r="210" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -13519,8 +14465,12 @@
       <c r="BD210" s="3"/>
       <c r="BE210" s="3"/>
       <c r="BF210" s="3"/>
-    </row>
-    <row r="211" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG210" s="3"/>
+      <c r="BH210" s="3"/>
+      <c r="BI210" s="3"/>
+      <c r="BJ210" s="3"/>
+    </row>
+    <row r="211" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -13577,8 +14527,12 @@
       <c r="BD211" s="3"/>
       <c r="BE211" s="3"/>
       <c r="BF211" s="3"/>
-    </row>
-    <row r="212" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG211" s="3"/>
+      <c r="BH211" s="3"/>
+      <c r="BI211" s="3"/>
+      <c r="BJ211" s="3"/>
+    </row>
+    <row r="212" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -13635,8 +14589,12 @@
       <c r="BD212" s="3"/>
       <c r="BE212" s="3"/>
       <c r="BF212" s="3"/>
-    </row>
-    <row r="213" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG212" s="3"/>
+      <c r="BH212" s="3"/>
+      <c r="BI212" s="3"/>
+      <c r="BJ212" s="3"/>
+    </row>
+    <row r="213" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -13693,8 +14651,12 @@
       <c r="BD213" s="3"/>
       <c r="BE213" s="3"/>
       <c r="BF213" s="3"/>
-    </row>
-    <row r="214" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG213" s="3"/>
+      <c r="BH213" s="3"/>
+      <c r="BI213" s="3"/>
+      <c r="BJ213" s="3"/>
+    </row>
+    <row r="214" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -13751,8 +14713,12 @@
       <c r="BD214" s="3"/>
       <c r="BE214" s="3"/>
       <c r="BF214" s="3"/>
-    </row>
-    <row r="215" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG214" s="3"/>
+      <c r="BH214" s="3"/>
+      <c r="BI214" s="3"/>
+      <c r="BJ214" s="3"/>
+    </row>
+    <row r="215" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -13809,8 +14775,12 @@
       <c r="BD215" s="3"/>
       <c r="BE215" s="3"/>
       <c r="BF215" s="3"/>
-    </row>
-    <row r="216" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG215" s="3"/>
+      <c r="BH215" s="3"/>
+      <c r="BI215" s="3"/>
+      <c r="BJ215" s="3"/>
+    </row>
+    <row r="216" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -13867,8 +14837,12 @@
       <c r="BD216" s="3"/>
       <c r="BE216" s="3"/>
       <c r="BF216" s="3"/>
-    </row>
-    <row r="217" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG216" s="3"/>
+      <c r="BH216" s="3"/>
+      <c r="BI216" s="3"/>
+      <c r="BJ216" s="3"/>
+    </row>
+    <row r="217" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -13925,8 +14899,12 @@
       <c r="BD217" s="3"/>
       <c r="BE217" s="3"/>
       <c r="BF217" s="3"/>
-    </row>
-    <row r="218" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG217" s="3"/>
+      <c r="BH217" s="3"/>
+      <c r="BI217" s="3"/>
+      <c r="BJ217" s="3"/>
+    </row>
+    <row r="218" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -13983,8 +14961,12 @@
       <c r="BD218" s="3"/>
       <c r="BE218" s="3"/>
       <c r="BF218" s="3"/>
-    </row>
-    <row r="219" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG218" s="3"/>
+      <c r="BH218" s="3"/>
+      <c r="BI218" s="3"/>
+      <c r="BJ218" s="3"/>
+    </row>
+    <row r="219" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -14041,8 +15023,12 @@
       <c r="BD219" s="3"/>
       <c r="BE219" s="3"/>
       <c r="BF219" s="3"/>
-    </row>
-    <row r="220" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG219" s="3"/>
+      <c r="BH219" s="3"/>
+      <c r="BI219" s="3"/>
+      <c r="BJ219" s="3"/>
+    </row>
+    <row r="220" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -14099,8 +15085,12 @@
       <c r="BD220" s="3"/>
       <c r="BE220" s="3"/>
       <c r="BF220" s="3"/>
-    </row>
-    <row r="221" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG220" s="3"/>
+      <c r="BH220" s="3"/>
+      <c r="BI220" s="3"/>
+      <c r="BJ220" s="3"/>
+    </row>
+    <row r="221" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -14157,8 +15147,12 @@
       <c r="BD221" s="3"/>
       <c r="BE221" s="3"/>
       <c r="BF221" s="3"/>
-    </row>
-    <row r="222" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG221" s="3"/>
+      <c r="BH221" s="3"/>
+      <c r="BI221" s="3"/>
+      <c r="BJ221" s="3"/>
+    </row>
+    <row r="222" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -14215,8 +15209,12 @@
       <c r="BD222" s="3"/>
       <c r="BE222" s="3"/>
       <c r="BF222" s="3"/>
-    </row>
-    <row r="223" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG222" s="3"/>
+      <c r="BH222" s="3"/>
+      <c r="BI222" s="3"/>
+      <c r="BJ222" s="3"/>
+    </row>
+    <row r="223" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -14273,8 +15271,12 @@
       <c r="BD223" s="3"/>
       <c r="BE223" s="3"/>
       <c r="BF223" s="3"/>
-    </row>
-    <row r="224" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG223" s="3"/>
+      <c r="BH223" s="3"/>
+      <c r="BI223" s="3"/>
+      <c r="BJ223" s="3"/>
+    </row>
+    <row r="224" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -14331,8 +15333,12 @@
       <c r="BD224" s="3"/>
       <c r="BE224" s="3"/>
       <c r="BF224" s="3"/>
-    </row>
-    <row r="225" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG224" s="3"/>
+      <c r="BH224" s="3"/>
+      <c r="BI224" s="3"/>
+      <c r="BJ224" s="3"/>
+    </row>
+    <row r="225" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -14389,8 +15395,12 @@
       <c r="BD225" s="3"/>
       <c r="BE225" s="3"/>
       <c r="BF225" s="3"/>
-    </row>
-    <row r="226" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG225" s="3"/>
+      <c r="BH225" s="3"/>
+      <c r="BI225" s="3"/>
+      <c r="BJ225" s="3"/>
+    </row>
+    <row r="226" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -14447,8 +15457,12 @@
       <c r="BD226" s="3"/>
       <c r="BE226" s="3"/>
       <c r="BF226" s="3"/>
-    </row>
-    <row r="227" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG226" s="3"/>
+      <c r="BH226" s="3"/>
+      <c r="BI226" s="3"/>
+      <c r="BJ226" s="3"/>
+    </row>
+    <row r="227" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -14505,8 +15519,12 @@
       <c r="BD227" s="3"/>
       <c r="BE227" s="3"/>
       <c r="BF227" s="3"/>
-    </row>
-    <row r="228" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG227" s="3"/>
+      <c r="BH227" s="3"/>
+      <c r="BI227" s="3"/>
+      <c r="BJ227" s="3"/>
+    </row>
+    <row r="228" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -14563,8 +15581,12 @@
       <c r="BD228" s="3"/>
       <c r="BE228" s="3"/>
       <c r="BF228" s="3"/>
-    </row>
-    <row r="229" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG228" s="3"/>
+      <c r="BH228" s="3"/>
+      <c r="BI228" s="3"/>
+      <c r="BJ228" s="3"/>
+    </row>
+    <row r="229" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -14621,8 +15643,12 @@
       <c r="BD229" s="3"/>
       <c r="BE229" s="3"/>
       <c r="BF229" s="3"/>
-    </row>
-    <row r="230" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG229" s="3"/>
+      <c r="BH229" s="3"/>
+      <c r="BI229" s="3"/>
+      <c r="BJ229" s="3"/>
+    </row>
+    <row r="230" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -14679,8 +15705,12 @@
       <c r="BD230" s="3"/>
       <c r="BE230" s="3"/>
       <c r="BF230" s="3"/>
-    </row>
-    <row r="231" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG230" s="3"/>
+      <c r="BH230" s="3"/>
+      <c r="BI230" s="3"/>
+      <c r="BJ230" s="3"/>
+    </row>
+    <row r="231" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -14737,8 +15767,12 @@
       <c r="BD231" s="3"/>
       <c r="BE231" s="3"/>
       <c r="BF231" s="3"/>
-    </row>
-    <row r="232" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG231" s="3"/>
+      <c r="BH231" s="3"/>
+      <c r="BI231" s="3"/>
+      <c r="BJ231" s="3"/>
+    </row>
+    <row r="232" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -14795,8 +15829,12 @@
       <c r="BD232" s="3"/>
       <c r="BE232" s="3"/>
       <c r="BF232" s="3"/>
-    </row>
-    <row r="233" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG232" s="3"/>
+      <c r="BH232" s="3"/>
+      <c r="BI232" s="3"/>
+      <c r="BJ232" s="3"/>
+    </row>
+    <row r="233" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -14853,8 +15891,12 @@
       <c r="BD233" s="3"/>
       <c r="BE233" s="3"/>
       <c r="BF233" s="3"/>
-    </row>
-    <row r="234" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG233" s="3"/>
+      <c r="BH233" s="3"/>
+      <c r="BI233" s="3"/>
+      <c r="BJ233" s="3"/>
+    </row>
+    <row r="234" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -14911,8 +15953,12 @@
       <c r="BD234" s="3"/>
       <c r="BE234" s="3"/>
       <c r="BF234" s="3"/>
-    </row>
-    <row r="235" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG234" s="3"/>
+      <c r="BH234" s="3"/>
+      <c r="BI234" s="3"/>
+      <c r="BJ234" s="3"/>
+    </row>
+    <row r="235" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -14969,8 +16015,12 @@
       <c r="BD235" s="3"/>
       <c r="BE235" s="3"/>
       <c r="BF235" s="3"/>
-    </row>
-    <row r="236" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG235" s="3"/>
+      <c r="BH235" s="3"/>
+      <c r="BI235" s="3"/>
+      <c r="BJ235" s="3"/>
+    </row>
+    <row r="236" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -15027,8 +16077,12 @@
       <c r="BD236" s="3"/>
       <c r="BE236" s="3"/>
       <c r="BF236" s="3"/>
-    </row>
-    <row r="237" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG236" s="3"/>
+      <c r="BH236" s="3"/>
+      <c r="BI236" s="3"/>
+      <c r="BJ236" s="3"/>
+    </row>
+    <row r="237" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -15085,8 +16139,12 @@
       <c r="BD237" s="3"/>
       <c r="BE237" s="3"/>
       <c r="BF237" s="3"/>
-    </row>
-    <row r="238" spans="3:58" x14ac:dyDescent="0.2">
+      <c r="BG237" s="3"/>
+      <c r="BH237" s="3"/>
+      <c r="BI237" s="3"/>
+      <c r="BJ237" s="3"/>
+    </row>
+    <row r="238" spans="3:62" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -15143,6 +16201,10 @@
       <c r="BD238" s="3"/>
       <c r="BE238" s="3"/>
       <c r="BF238" s="3"/>
+      <c r="BG238" s="3"/>
+      <c r="BH238" s="3"/>
+      <c r="BI238" s="3"/>
+      <c r="BJ238" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
